--- a/data/Club_domiciliation.xlsx
+++ b/data/Club_domiciliation.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Feuille2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="555">
   <si>
     <t>Club</t>
   </si>
@@ -864,7 +864,823 @@
     <t xml:space="preserve">BOWLING CLUB O-277</t>
   </si>
   <si>
-    <t>BOWL</t>
+    <t xml:space="preserve">BOWLING CLUB ORLEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB PAU BEARN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB PHOCEEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAN DE CAMPAGNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemin des Pennes au Pin, 13170 Les Pennes-Mirabeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB RODEZ ONET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB ROUEN LE DRAGON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB SAINT ETIENNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB SAINTAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB STRIKING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB THIAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB THONON LES BAINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB TRIANGLE D'OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB VAN GOGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING CLUB VOSGIEN GOLBEY</t>
+  </si>
+  <si>
+    <t>EPINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 Espace Saint Michel, 88000 Épinal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOWLING TOURS METROPOLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTRE DAME D'OE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Rue Olof Palme, 37390 Notre-Dame-d'Oé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSC WOLVES SAINT MAXIMIN CREIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST MAXIMIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone Artisanale du Bois des Fenêtres, 60740 Saint-Maximin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUDDY'S MBA -  REIMS TINQUEUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowling Club Douai Quai 121</t>
+  </si>
+  <si>
+    <t>DOUAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193 Boulevard Louis Breguet, 59500 Douai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowling Club Les Tontons Strikeurs 57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST JULIEN LES METZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 Avenue Paul Langevin, 57070 Saint-Julien-lès-Metz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'CHARTRES  BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D.  DROME-ARDECHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE L'EURE ET LOIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE L'HERAULT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE L'INDRE ET LOIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE L'YONNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA CHARENTE MARITIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA COTE D'OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA DORDOGNE</t>
+  </si>
+  <si>
+    <t>BERGERAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Zone de Loisirs, Route de Bordeaux, 24100 Bergerac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA GIRONDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA HAUTE SAVOIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA MEURTHE ET MOSELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DE LA MOSELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DES LANDES</t>
+  </si>
+  <si>
+    <t>YZOSSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">740 Route de Montfort, 40180 Yzosse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU BAS RHIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU CHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST DOULCHARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route d'Orléans, 18230 Saint-Doulchard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU GARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU HAUT RHIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU LOIRET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU NORD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU PAS DE CALAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D. DU RHONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.D.A WIZARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.S.G. BOWLING NOTRE DAME DE GRAVENCHON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTRE DAME DE GRAVENCHON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Rue Jean Maridor, 76330 Notre-Dame-de-Gravenchon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANIBALS PERPIGNAN BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>RIVESALTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue Henri Chrétien, Centre Commercial Cap Roussillon, 66600 Rivesaltes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANONNIERS MONTAUBAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARPE DIEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHABLAIS BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>CHALLENGER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHALON BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>TORCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du Vieux Port, 71210 Torcy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARDON LORRAIN BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAROLAIS BULLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAURAY BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>CHAURAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 Rue Gay-Lussac, 79180 Chauray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHORUS BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB AUDIN BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB BOWL'MAINE SABLE SUR SARTHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB BOWLING CHAUMONTAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB BOWLING LA GIGNACOISE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB OMNISPORTS BRGM ORLEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLUB RN 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRA 18 BOURGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRA ANGERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COGNAC STRIKE BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>COGNAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Rue du Commerce, 16100 Châteaubernard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRE X SPARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRAZY BOWLERS BC CHELLES</t>
+  </si>
+  <si>
+    <t>DIABOWLIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRAGON BOWL BAYEUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.S.C.A.A.M. LE MANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAGLES BOWLING VIRE</t>
+  </si>
+  <si>
+    <t>VIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue de la Petite-Vitesse, 14500 Vire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAGLES WITTELSHEIM</t>
+  </si>
+  <si>
+    <t>ECLATS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE CLUB BLACK CAT</t>
+  </si>
+  <si>
+    <t>ALBERTVILLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115 Chemin du Pont Albertin, 73200 Albertville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE CLUB BOWLING PUY EN VELAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE CLUB LAGUNEKIN BAYONNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING AVERMES-MOULINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOULINS - L'ENJOY-AVERMES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemin des Maisons Neuves, 03000 Avermes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING D'ARGENTAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE CHERBOURG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE DRAGUIGNAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE MARTIGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE RODEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE SAINT LO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING DE TOULOUSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING ESPACE JEUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING LIMOGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING PERPIGNAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING SKITTLE BELFORT</t>
+  </si>
+  <si>
+    <t>BELFORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue de l'As de Carreau, Centre commercial des 4 AS, 90000 Belfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE DE BOWLING STE FOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOLE-CLUB DE BOWLING DE CANET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTENTE SPORTIVE RENAULT GROUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESAM LES MUREAUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPACE BOWLING CLUB NARBONNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURO BOWLING FLANDRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUROPEEN B.C. THIONVILLOIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIREBOWL ORLEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLERS BOWLING IMPACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONTAINE BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONTAINE LE COMTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue du Vercors, ZA Les Brandes, 86240 Fontaine-le-Comte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORCE CINÉTIQUE STONES IDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRIEND'S BOWLING ACADEMY PARIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUN BOWLERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUN BOWLING CLUB LES HERBIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES HERBIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Avenue du Bocage, 85500 Les Herbiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAZELEC SPORTS CÔTES D'ARMOR Section Bowling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLADIATORES NEMAUSENSIS GN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUADELOUPE BOWLING ASSOCIATION</t>
+  </si>
+  <si>
+    <t>GUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HER BOWLING 201</t>
+  </si>
+  <si>
+    <t>IFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEUNES STRIKERS CHÂLONNAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOCK CHANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARUKERA STRIKE ASSOCIATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KINGS &amp; QUEENS CBA REIMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KINGS BOWLING CLUB LAON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE STRIKE CLUB AUBENAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEOPARDS GRAND QUEVILLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES AIGLES 85 B.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES AMIS DU YETI BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES CIGALES BOWLERS DE PERTUIS</t>
+  </si>
+  <si>
+    <t>PERTUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">477 Rue Saint-Martin, 84120 Pertuis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES COBRAS DE KRAFFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES DRAGONS DE COLMAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES ECHELLES BLEUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES FORGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES GAILLARDS DE BRIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES GUNNER'S BOURGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES LEOPARDS CAEN-NORMANDIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES LEZARDS DE MONTIVILLIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES LIONCEAUX DIJON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES PIRATES D'ALENCON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES SNIPER'S DE WITTELSHEIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES SPARTANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES SPEED BOWLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LES WILDCATS DE MULHOUSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESCAR BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE REGIONALE    BOURGOGNE FRANCHE COMTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE REGIONALE AUVERGNE RHONE ALPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE REGIONALE GRAND EST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE REGIONALE ILE DE FRANCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE REGIONALE PACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE RÉGIONALE BRETAGNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGUE RÉGIONALE NOUVELLE AQUITAINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LITTORAL BC GRAVELINES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCKY BOWL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCKY STRIKER'S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCON BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACON BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCEY LES GREVES CLUB - MGC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESCHERS BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MESCHERS SUR GIRONDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 Route de Semussac, 17132 Meschers-sur-Gironde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONACO BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW TEAM B.C. MARTIGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW WAVE BOWLING LA ROCHELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICE ACROPOLIS S.B.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICE COTE D'AZUR BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODET B.C. QUIMPER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLYMPIC BOWLING CLUB DE MILLAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSPARE BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAC MAN NANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRONAGE LAIQUE LORIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRONAGE LAÏQUE ARGENTAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAU BCA 64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERTUIS CLUB BOWLING SAINT BARTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHINIA ROTO-SPORTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHOENIX BOWLERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHOENIX CLUB BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN BULLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHALONS EN CHAMPAGNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue Michel Ménard, 51000 Châlons-en-Champagne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLYGONE BOWLING CLUB BEZIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESQU'ILE BOWLING CLUB</t>
+  </si>
+  <si>
+    <t>PROMOSTARS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.C.T. BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED BOWL BUXEROLLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED WOLVES AIX LES BAINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAMBERY VOGLANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rue de la Françon, 73420 Voglans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROAZHON BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROCKETS NANTES</t>
+  </si>
+  <si>
+    <t>ROLLIN'BOWL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S C B D'AGENAIS</t>
+  </si>
+  <si>
+    <t>AGEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88 Avenue de Bigorre, 47550 Boé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S P U C  PESSAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.B.A.C. CLERMONT FERRAND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.Q. TOULOUSAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINT BRIEUC BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINT PAUL SPORTS BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINT-QUENTIN BUL'S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORPIONS BOWLING</t>
+  </si>
+  <si>
+    <t>SHARKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKITTLE CLUB FRANCHE COMTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLUC NANCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMOC BOWLING ST-JEAN DE BRAYE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNIPERS NANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPACE BOWLERS VICHY CUSSET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPACEBOWL - CUSSET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Rue Ampère, ZI de Cusset, 03300 Cusset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPORTING BOWL CHAMBERY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPORTS CG41 SECTION BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQUALES BC CREIL- ST MAXIMIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST MAX BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STARBOWLERS AVERMES-MOULINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STELLANTIS ATHLETIC CLUB DE CHARLEVILLE-MEZIERES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKE 40 YZOSSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKE 59 VILLENEUVE D'ASCQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLENEUVE D'ASCQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Rue des Vétérans, 59650 Villeneuve-d'Ascq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKE BACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKE BALL BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKE CLUB AVERMES MOULINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKERS BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKES &amp; SPARES AVIGNON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRIKES SHOOTERS AGEN BOWLING TEAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNERGIE BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.O.A.C. TOULOUSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAMS BOWLING BERGERAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE BULL BOWL'S BOURGES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOP GONES LYON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOULOUSE BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANQUILLES NOUVELLE AQUITAINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TROYES GYMNIQUE BOWLING</t>
+  </si>
+  <si>
+    <t>TROYES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Rue des Bas Trévois, 10000 Troyes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.C.S. BOWLING COSNE SUR LOIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNION SPORTIVE ORLEANAISE BOWLING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USC DCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UST BOWLING ST TROPEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UZES BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENCIENNES BOWLING CLUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALHALLA VIRE NORMANDIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINNER'S ORLEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOLVES BOWLING BLOIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X BOWL BARJOUVILLE</t>
+  </si>
+  <si>
+    <t>X-STRIKES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XBS CINETIC PARIS</t>
   </si>
 </sst>
 </file>
@@ -1398,17 +2214,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="46.28125"/>
+    <col bestFit="1" min="1" max="1" width="47.00390625"/>
     <col bestFit="1" min="2" max="2" width="6.57421875"/>
+    <col bestFit="1" min="3" max="3" width="16.7109375"/>
+    <col bestFit="1" min="4" max="4" width="10.7109375"/>
     <col bestFit="1" min="5" max="5" width="30.57421875"/>
-    <col bestFit="1" min="6" max="6" width="55.28125"/>
+    <col bestFit="1" min="6" max="6" width="61.7109375"/>
     <col bestFit="1" min="7" max="7" width="19.8515625"/>
     <col bestFit="1" min="8" max="8" width="42.57421875"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1434,7 +2252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1452,7 +2270,7 @@
       <c r="G2"/>
       <c r="H2"/>
     </row>
-    <row r="3" ht="14.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1478,7 +2296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="14.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1504,7 +2322,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1530,7 +2348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="14.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1548,7 +2366,7 @@
       <c r="G6"/>
       <c r="H6"/>
     </row>
-    <row r="7" ht="14.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1574,7 +2392,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" ht="14.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1600,7 +2418,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="14.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1626,7 +2444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1652,7 +2470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1678,7 +2496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1696,7 +2514,7 @@
       <c r="G12"/>
       <c r="H12"/>
     </row>
-    <row r="13" ht="14.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1722,7 +2540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1748,7 +2566,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1774,7 +2592,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -1800,7 +2618,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" ht="14.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1826,7 +2644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" ht="14.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -1844,7 +2662,7 @@
       <c r="G18"/>
       <c r="H18"/>
     </row>
-    <row r="19" ht="14.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -1870,7 +2688,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" ht="14.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1896,7 +2714,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" ht="14.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -1914,7 +2732,7 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" ht="14.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -1940,7 +2758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" ht="14.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>72</v>
       </c>
@@ -1966,7 +2784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" ht="14.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -1992,7 +2810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" ht="14.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -2018,7 +2836,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" ht="14.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -2044,7 +2862,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" ht="14.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -2070,7 +2888,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" ht="14.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -2096,7 +2914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" ht="14.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -2122,7 +2940,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" ht="14.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -2148,7 +2966,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="14.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -2174,7 +2992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" ht="14.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -2200,7 +3018,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" ht="14.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -2226,7 +3044,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" ht="14.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>92</v>
       </c>
@@ -2252,7 +3070,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="14.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -2278,7 +3096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" ht="14.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>99</v>
       </c>
@@ -2304,7 +3122,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" ht="14.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>102</v>
       </c>
@@ -2330,7 +3148,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" ht="14.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>105</v>
       </c>
@@ -2356,7 +3174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" ht="14.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>108</v>
       </c>
@@ -2382,7 +3200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" ht="14.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -2408,7 +3226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" ht="14.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -2434,7 +3252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" ht="14.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -2460,7 +3278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" ht="14.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -2478,7 +3296,7 @@
       <c r="G43"/>
       <c r="H43"/>
     </row>
-    <row r="44" ht="14.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -2504,7 +3322,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="14.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>121</v>
       </c>
@@ -2530,7 +3348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="14.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>124</v>
       </c>
@@ -2556,7 +3374,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" ht="14.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>125</v>
       </c>
@@ -2582,7 +3400,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="14.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>128</v>
       </c>
@@ -2608,7 +3426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" ht="14.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>131</v>
       </c>
@@ -2634,7 +3452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" ht="14.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>134</v>
       </c>
@@ -2660,7 +3478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" ht="14.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>135</v>
       </c>
@@ -2686,7 +3504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" ht="14.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>136</v>
       </c>
@@ -2704,7 +3522,7 @@
       <c r="G52"/>
       <c r="H52"/>
     </row>
-    <row r="53" ht="14.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>137</v>
       </c>
@@ -2730,7 +3548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" ht="14.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>138</v>
       </c>
@@ -2748,7 +3566,7 @@
       <c r="G54"/>
       <c r="H54"/>
     </row>
-    <row r="55" ht="14.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>139</v>
       </c>
@@ -2774,7 +3592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" ht="14.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -2800,7 +3618,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" ht="14.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>141</v>
       </c>
@@ -2826,7 +3644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" ht="14.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>144</v>
       </c>
@@ -2852,7 +3670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" ht="14.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>148</v>
       </c>
@@ -2878,7 +3696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" ht="14.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>151</v>
       </c>
@@ -2904,7 +3722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" ht="14.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>154</v>
       </c>
@@ -2930,7 +3748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" ht="14.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>155</v>
       </c>
@@ -2956,7 +3774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" ht="14.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>158</v>
       </c>
@@ -2982,7 +3800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" ht="14.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>161</v>
       </c>
@@ -3008,7 +3826,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" ht="14.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>162</v>
       </c>
@@ -3034,7 +3852,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" ht="14.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>165</v>
       </c>
@@ -3060,7 +3878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" ht="14.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>166</v>
       </c>
@@ -3086,7 +3904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" ht="14.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>167</v>
       </c>
@@ -3104,7 +3922,7 @@
       <c r="G68"/>
       <c r="H68"/>
     </row>
-    <row r="69" ht="14.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>168</v>
       </c>
@@ -3130,7 +3948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" ht="14.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>171</v>
       </c>
@@ -3156,7 +3974,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" ht="14.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>172</v>
       </c>
@@ -3182,7 +4000,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" ht="14.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>173</v>
       </c>
@@ -3208,7 +4026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" ht="14.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>174</v>
       </c>
@@ -3234,7 +4052,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" ht="14.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>175</v>
       </c>
@@ -3260,7 +4078,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" ht="14.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>176</v>
       </c>
@@ -3286,7 +4104,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" ht="14.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>177</v>
       </c>
@@ -3312,7 +4130,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" ht="14.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>180</v>
       </c>
@@ -3338,7 +4156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" ht="14.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>183</v>
       </c>
@@ -3364,7 +4182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" ht="14.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>186</v>
       </c>
@@ -3390,7 +4208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" ht="14.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>189</v>
       </c>
@@ -3416,7 +4234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" ht="14.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>192</v>
       </c>
@@ -3442,7 +4260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" ht="14.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>195</v>
       </c>
@@ -3468,7 +4286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" ht="14.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>196</v>
       </c>
@@ -3494,7 +4312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" ht="14.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>197</v>
       </c>
@@ -3520,7 +4338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" ht="14.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>200</v>
       </c>
@@ -3546,7 +4364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" ht="14.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>203</v>
       </c>
@@ -3572,7 +4390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" ht="14.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>204</v>
       </c>
@@ -3590,7 +4408,7 @@
       <c r="G87"/>
       <c r="H87"/>
     </row>
-    <row r="88" ht="14.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>205</v>
       </c>
@@ -3616,7 +4434,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" ht="14.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>208</v>
       </c>
@@ -3642,7 +4460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" ht="14.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -3668,7 +4486,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" ht="14.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>212</v>
       </c>
@@ -3694,7 +4512,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" ht="14.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>215</v>
       </c>
@@ -3720,7 +4538,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" ht="14.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>218</v>
       </c>
@@ -3746,7 +4564,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" ht="14.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>221</v>
       </c>
@@ -3772,7 +4590,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" ht="14.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>222</v>
       </c>
@@ -3798,7 +4616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" ht="14.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>225</v>
       </c>
@@ -3816,7 +4634,7 @@
       <c r="G96"/>
       <c r="H96"/>
     </row>
-    <row r="97" ht="14.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>226</v>
       </c>
@@ -3842,7 +4660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" ht="14.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>229</v>
       </c>
@@ -3868,7 +4686,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="99" ht="14.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>232</v>
       </c>
@@ -3894,7 +4712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" ht="14.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>233</v>
       </c>
@@ -3920,7 +4738,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" ht="14.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>236</v>
       </c>
@@ -3946,7 +4764,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" ht="14.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>239</v>
       </c>
@@ -3972,7 +4790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" ht="14.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>240</v>
       </c>
@@ -3998,7 +4816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" ht="14.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>241</v>
       </c>
@@ -4024,7 +4842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" ht="14.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>244</v>
       </c>
@@ -4050,7 +4868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" ht="14.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>245</v>
       </c>
@@ -4076,7 +4894,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" ht="14.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>248</v>
       </c>
@@ -4102,7 +4920,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" ht="14.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>251</v>
       </c>
@@ -4128,7 +4946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="109" ht="14.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>254</v>
       </c>
@@ -4154,7 +4972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" ht="14.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>255</v>
       </c>
@@ -4180,7 +4998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" ht="14.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>258</v>
       </c>
@@ -4206,7 +5024,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" ht="14.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>259</v>
       </c>
@@ -4232,7 +5050,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" ht="14.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>262</v>
       </c>
@@ -4258,7 +5076,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" ht="14.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>265</v>
       </c>
@@ -4284,7 +5102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" ht="14.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>268</v>
       </c>
@@ -4310,7 +5128,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" ht="14.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>269</v>
       </c>
@@ -4336,7 +5154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" ht="14.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>270</v>
       </c>
@@ -4362,7 +5180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" ht="14.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>271</v>
       </c>
@@ -4388,7 +5206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" ht="14.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>272</v>
       </c>
@@ -4414,7 +5232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" ht="14.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>273</v>
       </c>
@@ -4432,7 +5250,7 @@
       <c r="G120"/>
       <c r="H120"/>
     </row>
-    <row r="121" ht="14.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>274</v>
       </c>
@@ -4458,7 +5276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" ht="14.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>275</v>
       </c>
@@ -4484,7 +5302,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" ht="14.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>276</v>
       </c>
@@ -4502,7 +5320,7 @@
       <c r="G123"/>
       <c r="H123"/>
     </row>
-    <row r="124" ht="14.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>277</v>
       </c>
@@ -4528,7 +5346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" ht="14.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>278</v>
       </c>
@@ -4554,7 +5372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" ht="14.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>279</v>
       </c>
@@ -4580,7 +5398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" ht="14.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>280</v>
       </c>
@@ -4606,7 +5424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" ht="14.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>281</v>
       </c>
@@ -4632,9 +5450,5428 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" ht="14.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>282</v>
+      </c>
+      <c r="B129" t="s">
+        <v>64</v>
+      </c>
+      <c r="C129">
+        <v>45</v>
+      </c>
+      <c r="D129">
+        <v>24</v>
+      </c>
+      <c r="E129" t="s">
+        <v>68</v>
+      </c>
+      <c r="F129" t="s">
+        <v>69</v>
+      </c>
+      <c r="G129">
+        <v>45</v>
+      </c>
+      <c r="H129" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>283</v>
+      </c>
+      <c r="B130" t="s">
+        <v>89</v>
+      </c>
+      <c r="C130">
+        <v>64</v>
+      </c>
+      <c r="D130">
+        <v>30</v>
+      </c>
+      <c r="E130" t="s">
+        <v>106</v>
+      </c>
+      <c r="F130" t="s">
+        <v>107</v>
+      </c>
+      <c r="G130">
+        <v>64</v>
+      </c>
+      <c r="H130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" t="s">
+        <v>31</v>
+      </c>
+      <c r="C131">
+        <v>13</v>
+      </c>
+      <c r="D131">
+        <v>5</v>
+      </c>
+      <c r="E131" t="s">
+        <v>285</v>
+      </c>
+      <c r="F131" t="s">
+        <v>286</v>
+      </c>
+      <c r="G131">
+        <v>13</v>
+      </c>
+      <c r="H131" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>287</v>
+      </c>
+      <c r="B132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C132">
+        <v>12</v>
+      </c>
+      <c r="D132">
+        <v>76</v>
+      </c>
+      <c r="E132" t="s">
+        <v>132</v>
+      </c>
+      <c r="F132" t="s">
+        <v>133</v>
+      </c>
+      <c r="G132">
+        <v>12</v>
+      </c>
+      <c r="H132" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" t="s">
+        <v>145</v>
+      </c>
+      <c r="C133">
+        <v>76</v>
+      </c>
+      <c r="D133">
+        <v>27</v>
+      </c>
+      <c r="E133" t="s">
+        <v>246</v>
+      </c>
+      <c r="F133" t="s">
+        <v>247</v>
+      </c>
+      <c r="G133">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134">
+        <v>42</v>
+      </c>
+      <c r="D134">
+        <v>22</v>
+      </c>
+      <c r="E134" t="s">
+        <v>234</v>
+      </c>
+      <c r="F134" t="s">
+        <v>235</v>
+      </c>
+      <c r="G134">
+        <v>42</v>
+      </c>
+      <c r="H134" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135">
+        <v>17</v>
+      </c>
+      <c r="D135">
+        <v>10</v>
+      </c>
+      <c r="E135" t="s">
+        <v>78</v>
+      </c>
+      <c r="F135" t="s">
+        <v>79</v>
+      </c>
+      <c r="G135">
+        <v>17</v>
+      </c>
+      <c r="H135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>291</v>
+      </c>
+      <c r="B136" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136">
+        <v>59</v>
+      </c>
+      <c r="D136">
+        <v>38</v>
+      </c>
+      <c r="E136" t="s">
+        <v>152</v>
+      </c>
+      <c r="F136" t="s">
+        <v>153</v>
+      </c>
+      <c r="G136">
+        <v>59</v>
+      </c>
+      <c r="H136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>292</v>
+      </c>
+      <c r="B137" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137">
+        <v>94</v>
+      </c>
+      <c r="D137">
+        <v>51</v>
+      </c>
+      <c r="E137" t="s">
+        <v>156</v>
+      </c>
+      <c r="F137" t="s">
+        <v>157</v>
+      </c>
+      <c r="G137">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>293</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138">
+        <v>74</v>
+      </c>
+      <c r="D138">
+        <v>5</v>
+      </c>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" t="s">
+        <v>145</v>
+      </c>
+      <c r="C139">
+        <v>76</v>
+      </c>
+      <c r="D139">
+        <v>29</v>
+      </c>
+      <c r="E139" t="s">
+        <v>246</v>
+      </c>
+      <c r="F139" t="s">
+        <v>247</v>
+      </c>
+      <c r="G139">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>295</v>
+      </c>
+      <c r="B140" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140">
+        <v>59</v>
+      </c>
+      <c r="D140">
+        <v>22</v>
+      </c>
+      <c r="E140" t="s">
+        <v>152</v>
+      </c>
+      <c r="F140" t="s">
+        <v>153</v>
+      </c>
+      <c r="G140">
+        <v>59</v>
+      </c>
+      <c r="H140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>296</v>
+      </c>
+      <c r="B141" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141">
+        <v>88</v>
+      </c>
+      <c r="D141">
+        <v>48</v>
+      </c>
+      <c r="E141" t="s">
+        <v>297</v>
+      </c>
+      <c r="F141" t="s">
+        <v>298</v>
+      </c>
+      <c r="G141">
+        <v>88</v>
+      </c>
+      <c r="H141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>299</v>
+      </c>
+      <c r="B142" t="s">
+        <v>64</v>
+      </c>
+      <c r="C142">
+        <v>37</v>
+      </c>
+      <c r="D142">
+        <v>89</v>
+      </c>
+      <c r="E142" t="s">
+        <v>300</v>
+      </c>
+      <c r="F142" t="s">
+        <v>301</v>
+      </c>
+      <c r="G142">
+        <v>37</v>
+      </c>
+      <c r="H142" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>302</v>
+      </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143">
+        <v>60</v>
+      </c>
+      <c r="D143">
+        <v>58</v>
+      </c>
+      <c r="E143" t="s">
+        <v>303</v>
+      </c>
+      <c r="F143" t="s">
+        <v>304</v>
+      </c>
+      <c r="G143">
+        <v>60</v>
+      </c>
+      <c r="H143" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>305</v>
+      </c>
+      <c r="B144" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144">
+        <v>51</v>
+      </c>
+      <c r="D144">
+        <v>16</v>
+      </c>
+      <c r="E144" t="s">
+        <v>206</v>
+      </c>
+      <c r="F144" t="s">
+        <v>207</v>
+      </c>
+      <c r="G144">
+        <v>51</v>
+      </c>
+      <c r="H144" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>306</v>
+      </c>
+      <c r="B145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145">
+        <v>59</v>
+      </c>
+      <c r="D145">
+        <v>39</v>
+      </c>
+      <c r="E145" t="s">
+        <v>307</v>
+      </c>
+      <c r="F145" t="s">
+        <v>308</v>
+      </c>
+      <c r="G145">
+        <v>59</v>
+      </c>
+      <c r="H145" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146">
+        <v>57</v>
+      </c>
+      <c r="D146">
+        <v>9</v>
+      </c>
+      <c r="E146" t="s">
+        <v>310</v>
+      </c>
+      <c r="F146" t="s">
+        <v>311</v>
+      </c>
+      <c r="G146">
+        <v>57</v>
+      </c>
+      <c r="H146" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>312</v>
+      </c>
+      <c r="B147" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147">
+        <v>28</v>
+      </c>
+      <c r="D147">
+        <v>12</v>
+      </c>
+      <c r="E147" t="s">
+        <v>65</v>
+      </c>
+      <c r="F147" t="s">
+        <v>66</v>
+      </c>
+      <c r="G147">
+        <v>28</v>
+      </c>
+      <c r="H147" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>313</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148">
+        <v>26</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+      <c r="E148" t="s">
+        <v>163</v>
+      </c>
+      <c r="F148" t="s">
+        <v>164</v>
+      </c>
+      <c r="G148">
+        <v>26</v>
+      </c>
+      <c r="H148" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>314</v>
+      </c>
+      <c r="B149" t="s">
+        <v>64</v>
+      </c>
+      <c r="C149">
+        <v>28</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
+        <v>65</v>
+      </c>
+      <c r="F149" t="s">
+        <v>66</v>
+      </c>
+      <c r="G149">
+        <v>28</v>
+      </c>
+      <c r="H149" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>315</v>
+      </c>
+      <c r="B150" t="s">
+        <v>109</v>
+      </c>
+      <c r="C150">
+        <v>34</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150" t="s">
+        <v>159</v>
+      </c>
+      <c r="F150" t="s">
+        <v>160</v>
+      </c>
+      <c r="G150">
+        <v>34</v>
+      </c>
+      <c r="H150" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>316</v>
+      </c>
+      <c r="B151" t="s">
+        <v>64</v>
+      </c>
+      <c r="C151">
+        <v>37</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151" t="s">
+        <v>300</v>
+      </c>
+      <c r="F151" t="s">
+        <v>301</v>
+      </c>
+      <c r="G151">
+        <v>37</v>
+      </c>
+      <c r="H151" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>317</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152">
+        <v>89</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>53</v>
+      </c>
+      <c r="F152" t="s">
+        <v>54</v>
+      </c>
+      <c r="G152">
+        <v>89</v>
+      </c>
+      <c r="H152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>318</v>
+      </c>
+      <c r="B153" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153">
+        <v>17</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153" t="s">
+        <v>78</v>
+      </c>
+      <c r="F153" t="s">
+        <v>79</v>
+      </c>
+      <c r="G153">
+        <v>17</v>
+      </c>
+      <c r="H153" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>319</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154">
+        <v>21</v>
+      </c>
+      <c r="D154">
+        <v>20</v>
+      </c>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154"/>
+      <c r="H154"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>320</v>
+      </c>
+      <c r="B155" t="s">
+        <v>89</v>
+      </c>
+      <c r="C155">
+        <v>24</v>
+      </c>
+      <c r="D155">
+        <v>2</v>
+      </c>
+      <c r="E155" t="s">
+        <v>321</v>
+      </c>
+      <c r="F155" t="s">
+        <v>322</v>
+      </c>
+      <c r="G155">
+        <v>24</v>
+      </c>
+      <c r="H155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>323</v>
+      </c>
+      <c r="B156" t="s">
+        <v>89</v>
+      </c>
+      <c r="C156">
+        <v>33</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156" t="s">
+        <v>90</v>
+      </c>
+      <c r="F156" t="s">
+        <v>91</v>
+      </c>
+      <c r="G156">
+        <v>33</v>
+      </c>
+      <c r="H156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>324</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157">
+        <v>74</v>
+      </c>
+      <c r="D157">
+        <v>2</v>
+      </c>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>325</v>
+      </c>
+      <c r="B158" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158">
+        <v>54</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>326</v>
+      </c>
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159">
+        <v>57</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159" t="s">
+        <v>310</v>
+      </c>
+      <c r="F159" t="s">
+        <v>311</v>
+      </c>
+      <c r="G159">
+        <v>57</v>
+      </c>
+      <c r="H159" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>327</v>
+      </c>
+      <c r="B160" t="s">
+        <v>89</v>
+      </c>
+      <c r="C160">
+        <v>40</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160" t="s">
+        <v>328</v>
+      </c>
+      <c r="F160" t="s">
+        <v>329</v>
+      </c>
+      <c r="G160">
+        <v>40</v>
+      </c>
+      <c r="H160" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>330</v>
+      </c>
+      <c r="B161" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161">
+        <v>67</v>
+      </c>
+      <c r="D161">
+        <v>17</v>
+      </c>
+      <c r="E161" t="s">
+        <v>227</v>
+      </c>
+      <c r="F161" t="s">
+        <v>228</v>
+      </c>
+      <c r="G161">
+        <v>67</v>
+      </c>
+      <c r="H161" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>331</v>
+      </c>
+      <c r="B162" t="s">
+        <v>64</v>
+      </c>
+      <c r="C162">
+        <v>18</v>
+      </c>
+      <c r="D162">
+        <v>3</v>
+      </c>
+      <c r="E162" t="s">
+        <v>332</v>
+      </c>
+      <c r="F162" t="s">
+        <v>333</v>
+      </c>
+      <c r="G162">
+        <v>18</v>
+      </c>
+      <c r="H162" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>334</v>
+      </c>
+      <c r="B163" t="s">
+        <v>109</v>
+      </c>
+      <c r="C163">
+        <v>30</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+      <c r="E163" t="s">
+        <v>190</v>
+      </c>
+      <c r="F163" t="s">
+        <v>191</v>
+      </c>
+      <c r="G163">
+        <v>30</v>
+      </c>
+      <c r="H163" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>335</v>
+      </c>
+      <c r="B164" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164">
+        <v>68</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164" t="s">
+        <v>149</v>
+      </c>
+      <c r="F164" t="s">
+        <v>150</v>
+      </c>
+      <c r="G164">
+        <v>68</v>
+      </c>
+      <c r="H164" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>336</v>
+      </c>
+      <c r="B165" t="s">
+        <v>64</v>
+      </c>
+      <c r="C165">
+        <v>45</v>
+      </c>
+      <c r="D165">
+        <v>3</v>
+      </c>
+      <c r="E165" t="s">
+        <v>68</v>
+      </c>
+      <c r="F165" t="s">
+        <v>69</v>
+      </c>
+      <c r="G165">
+        <v>45</v>
+      </c>
+      <c r="H165" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>337</v>
+      </c>
+      <c r="B166" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166">
+        <v>59</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166" t="s">
+        <v>152</v>
+      </c>
+      <c r="F166" t="s">
+        <v>153</v>
+      </c>
+      <c r="G166">
+        <v>59</v>
+      </c>
+      <c r="H166" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>338</v>
+      </c>
+      <c r="B167" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167">
+        <v>62</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167"/>
+      <c r="F167"/>
+      <c r="G167"/>
+      <c r="H167"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>339</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168">
+        <v>69</v>
+      </c>
+      <c r="D168">
+        <v>3</v>
+      </c>
+      <c r="E168" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168">
+        <v>69</v>
+      </c>
+      <c r="H168" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>340</v>
+      </c>
+      <c r="B169" t="s">
+        <v>35</v>
+      </c>
+      <c r="C169">
+        <v>94</v>
+      </c>
+      <c r="D169">
+        <v>12</v>
+      </c>
+      <c r="E169" t="s">
+        <v>156</v>
+      </c>
+      <c r="F169" t="s">
+        <v>157</v>
+      </c>
+      <c r="G169">
+        <v>94</v>
+      </c>
+      <c r="H169" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>341</v>
+      </c>
+      <c r="B170" t="s">
+        <v>145</v>
+      </c>
+      <c r="C170">
+        <v>76</v>
+      </c>
+      <c r="D170">
+        <v>37</v>
+      </c>
+      <c r="E170" t="s">
+        <v>342</v>
+      </c>
+      <c r="F170" t="s">
+        <v>343</v>
+      </c>
+      <c r="G170">
+        <v>76</v>
+      </c>
+      <c r="H170" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>344</v>
+      </c>
+      <c r="B171" t="s">
+        <v>109</v>
+      </c>
+      <c r="C171">
+        <v>66</v>
+      </c>
+      <c r="D171">
+        <v>44</v>
+      </c>
+      <c r="E171" t="s">
+        <v>345</v>
+      </c>
+      <c r="F171" t="s">
+        <v>346</v>
+      </c>
+      <c r="G171">
+        <v>66</v>
+      </c>
+      <c r="H171" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>347</v>
+      </c>
+      <c r="B172" t="s">
+        <v>109</v>
+      </c>
+      <c r="C172">
+        <v>82</v>
+      </c>
+      <c r="D172">
+        <v>5</v>
+      </c>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172"/>
+      <c r="H172"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173">
+        <v>62</v>
+      </c>
+      <c r="D173">
+        <v>59</v>
+      </c>
+      <c r="E173"/>
+      <c r="F173"/>
+      <c r="G173"/>
+      <c r="H173"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>349</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174">
+        <v>74</v>
+      </c>
+      <c r="D174">
+        <v>9</v>
+      </c>
+      <c r="E174"/>
+      <c r="F174"/>
+      <c r="G174"/>
+      <c r="H174"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>350</v>
+      </c>
+      <c r="B175" t="s">
+        <v>35</v>
+      </c>
+      <c r="C175">
+        <v>75</v>
+      </c>
+      <c r="D175">
+        <v>16</v>
+      </c>
+      <c r="E175" t="s">
+        <v>84</v>
+      </c>
+      <c r="F175" t="s">
+        <v>85</v>
+      </c>
+      <c r="G175">
+        <v>75</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>351</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176">
+        <v>71</v>
+      </c>
+      <c r="D176">
+        <v>25</v>
+      </c>
+      <c r="E176" t="s">
+        <v>352</v>
+      </c>
+      <c r="F176" t="s">
+        <v>353</v>
+      </c>
+      <c r="G176">
+        <v>71</v>
+      </c>
+      <c r="H176" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>354</v>
+      </c>
+      <c r="B177" t="s">
+        <v>25</v>
+      </c>
+      <c r="C177">
+        <v>54</v>
+      </c>
+      <c r="D177">
+        <v>22</v>
+      </c>
+      <c r="E177"/>
+      <c r="F177"/>
+      <c r="G177"/>
+      <c r="H177"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178">
+        <v>71</v>
+      </c>
+      <c r="D178">
+        <v>29</v>
+      </c>
+      <c r="E178" t="s">
+        <v>352</v>
+      </c>
+      <c r="F178" t="s">
+        <v>353</v>
+      </c>
+      <c r="G178">
+        <v>71</v>
+      </c>
+      <c r="H178" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>356</v>
+      </c>
+      <c r="B179" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179">
+        <v>79</v>
+      </c>
+      <c r="D179">
+        <v>56</v>
+      </c>
+      <c r="E179" t="s">
+        <v>357</v>
+      </c>
+      <c r="F179" t="s">
+        <v>358</v>
+      </c>
+      <c r="G179">
+        <v>79</v>
+      </c>
+      <c r="H179" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>359</v>
+      </c>
+      <c r="B180" t="s">
+        <v>145</v>
+      </c>
+      <c r="C180">
+        <v>76</v>
+      </c>
+      <c r="D180">
+        <v>43</v>
+      </c>
+      <c r="E180" t="s">
+        <v>246</v>
+      </c>
+      <c r="F180" t="s">
+        <v>247</v>
+      </c>
+      <c r="G180">
+        <v>76</v>
+      </c>
+      <c r="H180" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>360</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181">
+        <v>25</v>
+      </c>
+      <c r="D181">
+        <v>20</v>
+      </c>
+      <c r="E181" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" t="s">
+        <v>18</v>
+      </c>
+      <c r="G181">
+        <v>25</v>
+      </c>
+      <c r="H181" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>361</v>
+      </c>
+      <c r="B182" t="s">
+        <v>46</v>
+      </c>
+      <c r="C182">
+        <v>72</v>
+      </c>
+      <c r="D182">
+        <v>9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>260</v>
+      </c>
+      <c r="F182" t="s">
+        <v>261</v>
+      </c>
+      <c r="G182">
+        <v>72</v>
+      </c>
+      <c r="H182" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>362</v>
+      </c>
+      <c r="B183" t="s">
+        <v>25</v>
+      </c>
+      <c r="C183">
+        <v>52</v>
+      </c>
+      <c r="D183">
+        <v>17</v>
+      </c>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183"/>
+      <c r="H183"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>363</v>
+      </c>
+      <c r="B184" t="s">
+        <v>109</v>
+      </c>
+      <c r="C184">
+        <v>34</v>
+      </c>
+      <c r="D184">
+        <v>20</v>
+      </c>
+      <c r="E184" t="s">
+        <v>159</v>
+      </c>
+      <c r="F184" t="s">
+        <v>160</v>
+      </c>
+      <c r="G184">
+        <v>34</v>
+      </c>
+      <c r="H184" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>364</v>
+      </c>
+      <c r="B185" t="s">
+        <v>64</v>
+      </c>
+      <c r="C185">
+        <v>45</v>
+      </c>
+      <c r="D185">
+        <v>6</v>
+      </c>
+      <c r="E185" t="s">
+        <v>68</v>
+      </c>
+      <c r="F185" t="s">
+        <v>69</v>
+      </c>
+      <c r="G185">
+        <v>45</v>
+      </c>
+      <c r="H185" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>365</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186">
+        <v>21</v>
+      </c>
+      <c r="D186">
+        <v>9</v>
+      </c>
+      <c r="E186"/>
+      <c r="F186"/>
+      <c r="G186"/>
+      <c r="H186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>366</v>
+      </c>
+      <c r="B187" t="s">
+        <v>64</v>
+      </c>
+      <c r="C187">
+        <v>18</v>
+      </c>
+      <c r="D187">
+        <v>20</v>
+      </c>
+      <c r="E187" t="s">
+        <v>332</v>
+      </c>
+      <c r="F187" t="s">
+        <v>333</v>
+      </c>
+      <c r="G187">
+        <v>18</v>
+      </c>
+      <c r="H187" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>367</v>
+      </c>
+      <c r="B188" t="s">
+        <v>46</v>
+      </c>
+      <c r="C188">
+        <v>49</v>
+      </c>
+      <c r="D188">
+        <v>32</v>
+      </c>
+      <c r="E188" t="s">
+        <v>56</v>
+      </c>
+      <c r="F188" t="s">
+        <v>57</v>
+      </c>
+      <c r="G188">
+        <v>49</v>
+      </c>
+      <c r="H188" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>368</v>
+      </c>
+      <c r="B189" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189">
+        <v>16</v>
+      </c>
+      <c r="D189">
+        <v>20</v>
+      </c>
+      <c r="E189" t="s">
+        <v>369</v>
+      </c>
+      <c r="F189" t="s">
+        <v>370</v>
+      </c>
+      <c r="G189">
+        <v>16</v>
+      </c>
+      <c r="H189" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>371</v>
+      </c>
+      <c r="B190" t="s">
+        <v>25</v>
+      </c>
+      <c r="C190">
+        <v>88</v>
+      </c>
+      <c r="D190">
+        <v>8</v>
+      </c>
+      <c r="E190" t="s">
+        <v>297</v>
+      </c>
+      <c r="F190" t="s">
+        <v>298</v>
+      </c>
+      <c r="G190">
+        <v>88</v>
+      </c>
+      <c r="H190" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>372</v>
+      </c>
+      <c r="B191" t="s">
+        <v>35</v>
+      </c>
+      <c r="C191">
+        <v>77</v>
+      </c>
+      <c r="D191">
+        <v>19</v>
+      </c>
+      <c r="E191" t="s">
+        <v>50</v>
+      </c>
+      <c r="F191" t="s">
+        <v>51</v>
+      </c>
+      <c r="G191">
+        <v>77</v>
+      </c>
+      <c r="H191" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>373</v>
+      </c>
+      <c r="B192" t="s">
+        <v>64</v>
+      </c>
+      <c r="C192">
+        <v>28</v>
+      </c>
+      <c r="D192">
+        <v>5</v>
+      </c>
+      <c r="E192" t="s">
+        <v>65</v>
+      </c>
+      <c r="F192" t="s">
+        <v>66</v>
+      </c>
+      <c r="G192">
+        <v>28</v>
+      </c>
+      <c r="H192" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>374</v>
+      </c>
+      <c r="B193" t="s">
+        <v>145</v>
+      </c>
+      <c r="C193">
+        <v>14</v>
+      </c>
+      <c r="D193">
+        <v>18</v>
+      </c>
+      <c r="E193" t="s">
+        <v>216</v>
+      </c>
+      <c r="F193" t="s">
+        <v>217</v>
+      </c>
+      <c r="G193">
+        <v>14</v>
+      </c>
+      <c r="H193" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>375</v>
+      </c>
+      <c r="B194" t="s">
+        <v>46</v>
+      </c>
+      <c r="C194">
+        <v>72</v>
+      </c>
+      <c r="D194">
+        <v>7</v>
+      </c>
+      <c r="E194" t="s">
+        <v>260</v>
+      </c>
+      <c r="F194" t="s">
+        <v>261</v>
+      </c>
+      <c r="G194">
+        <v>72</v>
+      </c>
+      <c r="H194" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>376</v>
+      </c>
+      <c r="B195" t="s">
+        <v>145</v>
+      </c>
+      <c r="C195">
+        <v>14</v>
+      </c>
+      <c r="D195">
+        <v>28</v>
+      </c>
+      <c r="E195" t="s">
+        <v>377</v>
+      </c>
+      <c r="F195" t="s">
+        <v>378</v>
+      </c>
+      <c r="G195">
+        <v>14</v>
+      </c>
+      <c r="H195" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>379</v>
+      </c>
+      <c r="B196" t="s">
+        <v>25</v>
+      </c>
+      <c r="C196">
+        <v>68</v>
+      </c>
+      <c r="D196">
+        <v>18</v>
+      </c>
+      <c r="E196" t="s">
+        <v>149</v>
+      </c>
+      <c r="F196" t="s">
+        <v>150</v>
+      </c>
+      <c r="G196">
+        <v>68</v>
+      </c>
+      <c r="H196" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>380</v>
+      </c>
+      <c r="B197" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197">
+        <v>59</v>
+      </c>
+      <c r="D197">
+        <v>50</v>
+      </c>
+      <c r="E197" t="s">
+        <v>152</v>
+      </c>
+      <c r="F197" t="s">
+        <v>153</v>
+      </c>
+      <c r="G197">
+        <v>59</v>
+      </c>
+      <c r="H197" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>381</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198">
+        <v>73</v>
+      </c>
+      <c r="D198">
+        <v>52</v>
+      </c>
+      <c r="E198" t="s">
+        <v>382</v>
+      </c>
+      <c r="F198" t="s">
+        <v>383</v>
+      </c>
+      <c r="G198">
+        <v>73</v>
+      </c>
+      <c r="H198" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>384</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199">
+        <v>43</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199"/>
+      <c r="H199"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>385</v>
+      </c>
+      <c r="B200" t="s">
+        <v>89</v>
+      </c>
+      <c r="C200">
+        <v>64</v>
+      </c>
+      <c r="D200">
+        <v>19</v>
+      </c>
+      <c r="E200" t="s">
+        <v>178</v>
+      </c>
+      <c r="F200" t="s">
+        <v>179</v>
+      </c>
+      <c r="G200">
+        <v>64</v>
+      </c>
+      <c r="H200" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>386</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201">
+        <v>3</v>
+      </c>
+      <c r="D201">
+        <v>4</v>
+      </c>
+      <c r="E201" t="s">
+        <v>387</v>
+      </c>
+      <c r="F201" t="s">
+        <v>388</v>
+      </c>
+      <c r="G201">
+        <v>3</v>
+      </c>
+      <c r="H201" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>389</v>
+      </c>
+      <c r="B202" t="s">
+        <v>145</v>
+      </c>
+      <c r="C202">
+        <v>61</v>
+      </c>
+      <c r="D202">
+        <v>8</v>
+      </c>
+      <c r="E202" t="s">
+        <v>223</v>
+      </c>
+      <c r="F202" t="s">
+        <v>224</v>
+      </c>
+      <c r="G202">
+        <v>61</v>
+      </c>
+      <c r="H202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>390</v>
+      </c>
+      <c r="B203" t="s">
+        <v>145</v>
+      </c>
+      <c r="C203">
+        <v>50</v>
+      </c>
+      <c r="D203">
+        <v>14</v>
+      </c>
+      <c r="E203" t="s">
+        <v>146</v>
+      </c>
+      <c r="F203" t="s">
+        <v>147</v>
+      </c>
+      <c r="G203">
+        <v>50</v>
+      </c>
+      <c r="H203" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>391</v>
+      </c>
+      <c r="B204" t="s">
+        <v>31</v>
+      </c>
+      <c r="C204">
+        <v>83</v>
+      </c>
+      <c r="D204">
+        <v>7</v>
+      </c>
+      <c r="E204" t="s">
+        <v>32</v>
+      </c>
+      <c r="F204" t="s">
+        <v>33</v>
+      </c>
+      <c r="G204">
+        <v>83</v>
+      </c>
+      <c r="H204" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>392</v>
+      </c>
+      <c r="B205" t="s">
+        <v>31</v>
+      </c>
+      <c r="C205">
+        <v>13</v>
+      </c>
+      <c r="D205">
+        <v>17</v>
+      </c>
+      <c r="E205" t="s">
+        <v>285</v>
+      </c>
+      <c r="F205" t="s">
+        <v>286</v>
+      </c>
+      <c r="G205">
+        <v>13</v>
+      </c>
+      <c r="H205" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>393</v>
+      </c>
+      <c r="B206" t="s">
+        <v>109</v>
+      </c>
+      <c r="C206">
+        <v>12</v>
+      </c>
+      <c r="D206">
+        <v>7</v>
+      </c>
+      <c r="E206" t="s">
+        <v>132</v>
+      </c>
+      <c r="F206" t="s">
+        <v>133</v>
+      </c>
+      <c r="G206">
+        <v>12</v>
+      </c>
+      <c r="H206" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>394</v>
+      </c>
+      <c r="B207" t="s">
+        <v>145</v>
+      </c>
+      <c r="C207">
+        <v>50</v>
+      </c>
+      <c r="D207">
+        <v>44</v>
+      </c>
+      <c r="E207" t="s">
+        <v>146</v>
+      </c>
+      <c r="F207" t="s">
+        <v>147</v>
+      </c>
+      <c r="G207">
+        <v>50</v>
+      </c>
+      <c r="H207" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>395</v>
+      </c>
+      <c r="B208" t="s">
+        <v>109</v>
+      </c>
+      <c r="C208">
+        <v>31</v>
+      </c>
+      <c r="D208">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
+        <v>110</v>
+      </c>
+      <c r="F208" t="s">
+        <v>111</v>
+      </c>
+      <c r="G208">
+        <v>31</v>
+      </c>
+      <c r="H208" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>396</v>
+      </c>
+      <c r="B209" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209">
+        <v>80</v>
+      </c>
+      <c r="D209">
+        <v>27</v>
+      </c>
+      <c r="E209" t="s">
+        <v>42</v>
+      </c>
+      <c r="F209" t="s">
+        <v>43</v>
+      </c>
+      <c r="G209">
+        <v>80</v>
+      </c>
+      <c r="H209" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>397</v>
+      </c>
+      <c r="B210" t="s">
+        <v>20</v>
+      </c>
+      <c r="C210">
+        <v>87</v>
+      </c>
+      <c r="D210">
+        <v>26</v>
+      </c>
+      <c r="E210" t="s">
+        <v>21</v>
+      </c>
+      <c r="F210" t="s">
+        <v>22</v>
+      </c>
+      <c r="G210">
+        <v>87</v>
+      </c>
+      <c r="H210" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>398</v>
+      </c>
+      <c r="B211" t="s">
+        <v>109</v>
+      </c>
+      <c r="C211">
+        <v>66</v>
+      </c>
+      <c r="D211">
+        <v>27</v>
+      </c>
+      <c r="E211" t="s">
+        <v>345</v>
+      </c>
+      <c r="F211" t="s">
+        <v>346</v>
+      </c>
+      <c r="G211">
+        <v>66</v>
+      </c>
+      <c r="H211" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>399</v>
+      </c>
+      <c r="B212" t="s">
+        <v>16</v>
+      </c>
+      <c r="C212">
+        <v>90</v>
+      </c>
+      <c r="D212">
+        <v>15</v>
+      </c>
+      <c r="E212" t="s">
+        <v>400</v>
+      </c>
+      <c r="F212" t="s">
+        <v>401</v>
+      </c>
+      <c r="G212">
+        <v>90</v>
+      </c>
+      <c r="H212" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>402</v>
+      </c>
+      <c r="B213" t="s">
+        <v>89</v>
+      </c>
+      <c r="C213">
+        <v>33</v>
+      </c>
+      <c r="D213">
+        <v>10</v>
+      </c>
+      <c r="E213" t="s">
+        <v>90</v>
+      </c>
+      <c r="F213" t="s">
+        <v>91</v>
+      </c>
+      <c r="G213">
+        <v>33</v>
+      </c>
+      <c r="H213" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>403</v>
+      </c>
+      <c r="B214" t="s">
+        <v>109</v>
+      </c>
+      <c r="C214">
+        <v>66</v>
+      </c>
+      <c r="D214">
+        <v>11</v>
+      </c>
+      <c r="E214" t="s">
+        <v>345</v>
+      </c>
+      <c r="F214" t="s">
+        <v>346</v>
+      </c>
+      <c r="G214">
+        <v>66</v>
+      </c>
+      <c r="H214" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>404</v>
+      </c>
+      <c r="B215" t="s">
+        <v>35</v>
+      </c>
+      <c r="C215">
+        <v>78</v>
+      </c>
+      <c r="D215">
+        <v>3</v>
+      </c>
+      <c r="E215" t="s">
+        <v>36</v>
+      </c>
+      <c r="F215" t="s">
+        <v>37</v>
+      </c>
+      <c r="G215">
+        <v>78</v>
+      </c>
+      <c r="H215" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>405</v>
+      </c>
+      <c r="B216" t="s">
+        <v>35</v>
+      </c>
+      <c r="C216">
+        <v>78</v>
+      </c>
+      <c r="D216">
+        <v>8</v>
+      </c>
+      <c r="E216" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" t="s">
+        <v>37</v>
+      </c>
+      <c r="G216">
+        <v>78</v>
+      </c>
+      <c r="H216" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>406</v>
+      </c>
+      <c r="B217" t="s">
+        <v>109</v>
+      </c>
+      <c r="C217">
+        <v>11</v>
+      </c>
+      <c r="D217">
+        <v>22</v>
+      </c>
+      <c r="E217" t="s">
+        <v>219</v>
+      </c>
+      <c r="F217" t="s">
+        <v>220</v>
+      </c>
+      <c r="G217">
+        <v>11</v>
+      </c>
+      <c r="H217" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>407</v>
+      </c>
+      <c r="B218" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218">
+        <v>59</v>
+      </c>
+      <c r="D218">
+        <v>22</v>
+      </c>
+      <c r="E218" t="s">
+        <v>152</v>
+      </c>
+      <c r="F218" t="s">
+        <v>153</v>
+      </c>
+      <c r="G218">
+        <v>59</v>
+      </c>
+      <c r="H218" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>408</v>
+      </c>
+      <c r="B219" t="s">
+        <v>25</v>
+      </c>
+      <c r="C219">
+        <v>57</v>
+      </c>
+      <c r="D219">
+        <v>78</v>
+      </c>
+      <c r="E219" t="s">
+        <v>310</v>
+      </c>
+      <c r="F219" t="s">
+        <v>311</v>
+      </c>
+      <c r="G219">
+        <v>57</v>
+      </c>
+      <c r="H219" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>409</v>
+      </c>
+      <c r="B220" t="s">
+        <v>64</v>
+      </c>
+      <c r="C220">
+        <v>45</v>
+      </c>
+      <c r="D220">
+        <v>31</v>
+      </c>
+      <c r="E220" t="s">
+        <v>68</v>
+      </c>
+      <c r="F220" t="s">
+        <v>69</v>
+      </c>
+      <c r="G220">
+        <v>45</v>
+      </c>
+      <c r="H220" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>410</v>
+      </c>
+      <c r="B221" t="s">
+        <v>145</v>
+      </c>
+      <c r="C221">
+        <v>61</v>
+      </c>
+      <c r="D221">
+        <v>12</v>
+      </c>
+      <c r="E221" t="s">
+        <v>223</v>
+      </c>
+      <c r="F221" t="s">
+        <v>224</v>
+      </c>
+      <c r="G221">
+        <v>61</v>
+      </c>
+      <c r="H221" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>411</v>
+      </c>
+      <c r="B222" t="s">
+        <v>20</v>
+      </c>
+      <c r="C222">
+        <v>86</v>
+      </c>
+      <c r="D222">
+        <v>34</v>
+      </c>
+      <c r="E222" t="s">
+        <v>412</v>
+      </c>
+      <c r="F222" t="s">
+        <v>413</v>
+      </c>
+      <c r="G222">
+        <v>86</v>
+      </c>
+      <c r="H222" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>414</v>
+      </c>
+      <c r="B223" t="s">
+        <v>35</v>
+      </c>
+      <c r="C223">
+        <v>95</v>
+      </c>
+      <c r="D223">
+        <v>34</v>
+      </c>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223"/>
+      <c r="H223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>415</v>
+      </c>
+      <c r="B224" t="s">
+        <v>35</v>
+      </c>
+      <c r="C224">
+        <v>75</v>
+      </c>
+      <c r="D224">
+        <v>66</v>
+      </c>
+      <c r="E224" t="s">
+        <v>84</v>
+      </c>
+      <c r="F224" t="s">
+        <v>85</v>
+      </c>
+      <c r="G224">
+        <v>75</v>
+      </c>
+      <c r="H224" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>416</v>
+      </c>
+      <c r="B225" t="s">
+        <v>64</v>
+      </c>
+      <c r="C225">
+        <v>45</v>
+      </c>
+      <c r="D225">
+        <v>81</v>
+      </c>
+      <c r="E225" t="s">
+        <v>68</v>
+      </c>
+      <c r="F225" t="s">
+        <v>69</v>
+      </c>
+      <c r="G225">
+        <v>45</v>
+      </c>
+      <c r="H225" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>417</v>
+      </c>
+      <c r="B226" t="s">
+        <v>46</v>
+      </c>
+      <c r="C226">
+        <v>85</v>
+      </c>
+      <c r="D226">
+        <v>30</v>
+      </c>
+      <c r="E226" t="s">
+        <v>418</v>
+      </c>
+      <c r="F226" t="s">
+        <v>419</v>
+      </c>
+      <c r="G226">
+        <v>85</v>
+      </c>
+      <c r="H226" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>420</v>
+      </c>
+      <c r="B227" t="s">
+        <v>93</v>
+      </c>
+      <c r="C227">
+        <v>22</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+      <c r="G227">
+        <v>22</v>
+      </c>
+      <c r="H227" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>421</v>
+      </c>
+      <c r="B228" t="s">
+        <v>109</v>
+      </c>
+      <c r="C228">
+        <v>30</v>
+      </c>
+      <c r="D228">
+        <v>31</v>
+      </c>
+      <c r="E228" t="s">
+        <v>190</v>
+      </c>
+      <c r="F228" t="s">
+        <v>191</v>
+      </c>
+      <c r="G228">
+        <v>30</v>
+      </c>
+      <c r="H228" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>422</v>
+      </c>
+      <c r="B229" t="s">
+        <v>423</v>
+      </c>
+      <c r="C229">
+        <v>971</v>
+      </c>
+      <c r="D229">
+        <v>14</v>
+      </c>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229"/>
+      <c r="H229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>424</v>
+      </c>
+      <c r="B230" t="s">
+        <v>46</v>
+      </c>
+      <c r="C230">
+        <v>85</v>
+      </c>
+      <c r="D230">
+        <v>29</v>
+      </c>
+      <c r="E230" t="s">
+        <v>47</v>
+      </c>
+      <c r="F230" t="s">
+        <v>48</v>
+      </c>
+      <c r="G230">
+        <v>85</v>
+      </c>
+      <c r="H230" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>425</v>
+      </c>
+      <c r="B231" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231">
+        <v>75</v>
+      </c>
+      <c r="D231">
+        <v>14</v>
+      </c>
+      <c r="E231" t="s">
+        <v>84</v>
+      </c>
+      <c r="F231" t="s">
+        <v>85</v>
+      </c>
+      <c r="G231">
+        <v>75</v>
+      </c>
+      <c r="H231" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>426</v>
+      </c>
+      <c r="B232" t="s">
+        <v>25</v>
+      </c>
+      <c r="C232">
+        <v>51</v>
+      </c>
+      <c r="D232">
+        <v>17</v>
+      </c>
+      <c r="E232" t="s">
+        <v>206</v>
+      </c>
+      <c r="F232" t="s">
+        <v>207</v>
+      </c>
+      <c r="G232">
+        <v>51</v>
+      </c>
+      <c r="H232" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>427</v>
+      </c>
+      <c r="B233" t="s">
+        <v>109</v>
+      </c>
+      <c r="C233">
+        <v>30</v>
+      </c>
+      <c r="D233">
+        <v>21</v>
+      </c>
+      <c r="E233" t="s">
+        <v>201</v>
+      </c>
+      <c r="F233" t="s">
+        <v>202</v>
+      </c>
+      <c r="G233">
+        <v>30</v>
+      </c>
+      <c r="H233" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>428</v>
+      </c>
+      <c r="B234" t="s">
+        <v>423</v>
+      </c>
+      <c r="C234">
+        <v>971</v>
+      </c>
+      <c r="D234">
+        <v>17</v>
+      </c>
+      <c r="E234"/>
+      <c r="F234"/>
+      <c r="G234"/>
+      <c r="H234"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>429</v>
+      </c>
+      <c r="B235" t="s">
+        <v>25</v>
+      </c>
+      <c r="C235">
+        <v>51</v>
+      </c>
+      <c r="D235">
+        <v>53</v>
+      </c>
+      <c r="E235" t="s">
+        <v>206</v>
+      </c>
+      <c r="F235" t="s">
+        <v>207</v>
+      </c>
+      <c r="G235">
+        <v>51</v>
+      </c>
+      <c r="H235" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>430</v>
+      </c>
+      <c r="B236" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236">
+        <v>2</v>
+      </c>
+      <c r="D236">
+        <v>13</v>
+      </c>
+      <c r="E236"/>
+      <c r="F236"/>
+      <c r="G236"/>
+      <c r="H236"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>431</v>
+      </c>
+      <c r="B237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237">
+        <v>7</v>
+      </c>
+      <c r="D237">
+        <v>5</v>
+      </c>
+      <c r="E237"/>
+      <c r="F237"/>
+      <c r="G237"/>
+      <c r="H237"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>432</v>
+      </c>
+      <c r="B238" t="s">
+        <v>145</v>
+      </c>
+      <c r="C238">
+        <v>76</v>
+      </c>
+      <c r="D238">
+        <v>57</v>
+      </c>
+      <c r="E238" t="s">
+        <v>246</v>
+      </c>
+      <c r="F238" t="s">
+        <v>247</v>
+      </c>
+      <c r="G238">
+        <v>76</v>
+      </c>
+      <c r="H238" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>433</v>
+      </c>
+      <c r="B239" t="s">
+        <v>46</v>
+      </c>
+      <c r="C239">
+        <v>85</v>
+      </c>
+      <c r="D239">
+        <v>28</v>
+      </c>
+      <c r="E239" t="s">
+        <v>47</v>
+      </c>
+      <c r="F239" t="s">
+        <v>48</v>
+      </c>
+      <c r="G239">
+        <v>85</v>
+      </c>
+      <c r="H239" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>434</v>
+      </c>
+      <c r="B240" t="s">
+        <v>145</v>
+      </c>
+      <c r="C240">
+        <v>50</v>
+      </c>
+      <c r="D240">
+        <v>14</v>
+      </c>
+      <c r="E240" t="s">
+        <v>146</v>
+      </c>
+      <c r="F240" t="s">
+        <v>147</v>
+      </c>
+      <c r="G240">
+        <v>50</v>
+      </c>
+      <c r="H240" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>435</v>
+      </c>
+      <c r="B241" t="s">
+        <v>31</v>
+      </c>
+      <c r="C241">
+        <v>84</v>
+      </c>
+      <c r="D241">
+        <v>67</v>
+      </c>
+      <c r="E241" t="s">
+        <v>436</v>
+      </c>
+      <c r="F241" t="s">
+        <v>437</v>
+      </c>
+      <c r="G241">
+        <v>84</v>
+      </c>
+      <c r="H241" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>438</v>
+      </c>
+      <c r="B242" t="s">
+        <v>25</v>
+      </c>
+      <c r="C242">
+        <v>67</v>
+      </c>
+      <c r="D242">
+        <v>17</v>
+      </c>
+      <c r="E242" t="s">
+        <v>227</v>
+      </c>
+      <c r="F242" t="s">
+        <v>228</v>
+      </c>
+      <c r="G242">
+        <v>67</v>
+      </c>
+      <c r="H242" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>439</v>
+      </c>
+      <c r="B243" t="s">
+        <v>25</v>
+      </c>
+      <c r="C243">
+        <v>68</v>
+      </c>
+      <c r="D243">
+        <v>43</v>
+      </c>
+      <c r="E243" t="s">
+        <v>149</v>
+      </c>
+      <c r="F243" t="s">
+        <v>150</v>
+      </c>
+      <c r="G243">
+        <v>68</v>
+      </c>
+      <c r="H243" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>440</v>
+      </c>
+      <c r="B244" t="s">
+        <v>64</v>
+      </c>
+      <c r="C244">
+        <v>45</v>
+      </c>
+      <c r="D244">
+        <v>6</v>
+      </c>
+      <c r="E244" t="s">
+        <v>68</v>
+      </c>
+      <c r="F244" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244">
+        <v>45</v>
+      </c>
+      <c r="H244" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>441</v>
+      </c>
+      <c r="B245" t="s">
+        <v>145</v>
+      </c>
+      <c r="C245">
+        <v>27</v>
+      </c>
+      <c r="D245">
+        <v>5</v>
+      </c>
+      <c r="E245" t="s">
+        <v>184</v>
+      </c>
+      <c r="F245" t="s">
+        <v>185</v>
+      </c>
+      <c r="G245">
+        <v>27</v>
+      </c>
+      <c r="H245" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>442</v>
+      </c>
+      <c r="B246" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246">
+        <v>19</v>
+      </c>
+      <c r="D246">
+        <v>8</v>
+      </c>
+      <c r="E246"/>
+      <c r="F246"/>
+      <c r="G246"/>
+      <c r="H246"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>443</v>
+      </c>
+      <c r="B247" t="s">
+        <v>64</v>
+      </c>
+      <c r="C247">
+        <v>18</v>
+      </c>
+      <c r="D247">
+        <v>6</v>
+      </c>
+      <c r="E247" t="s">
+        <v>332</v>
+      </c>
+      <c r="F247" t="s">
+        <v>333</v>
+      </c>
+      <c r="G247">
+        <v>18</v>
+      </c>
+      <c r="H247" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>444</v>
+      </c>
+      <c r="B248" t="s">
+        <v>145</v>
+      </c>
+      <c r="C248">
+        <v>14</v>
+      </c>
+      <c r="D248">
+        <v>12</v>
+      </c>
+      <c r="E248" t="s">
+        <v>377</v>
+      </c>
+      <c r="F248" t="s">
+        <v>378</v>
+      </c>
+      <c r="G248">
+        <v>14</v>
+      </c>
+      <c r="H248" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>445</v>
+      </c>
+      <c r="B249" t="s">
+        <v>145</v>
+      </c>
+      <c r="C249">
+        <v>76</v>
+      </c>
+      <c r="D249">
+        <v>11</v>
+      </c>
+      <c r="E249" t="s">
+        <v>246</v>
+      </c>
+      <c r="F249" t="s">
+        <v>247</v>
+      </c>
+      <c r="G249">
+        <v>76</v>
+      </c>
+      <c r="H249" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>446</v>
+      </c>
+      <c r="B250" t="s">
+        <v>16</v>
+      </c>
+      <c r="C250">
+        <v>21</v>
+      </c>
+      <c r="D250">
+        <v>39</v>
+      </c>
+      <c r="E250"/>
+      <c r="F250"/>
+      <c r="G250"/>
+      <c r="H250"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>447</v>
+      </c>
+      <c r="B251" t="s">
+        <v>46</v>
+      </c>
+      <c r="C251">
+        <v>72</v>
+      </c>
+      <c r="D251">
+        <v>11</v>
+      </c>
+      <c r="E251" t="s">
+        <v>260</v>
+      </c>
+      <c r="F251" t="s">
+        <v>261</v>
+      </c>
+      <c r="G251">
+        <v>72</v>
+      </c>
+      <c r="H251" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>448</v>
+      </c>
+      <c r="B252" t="s">
+        <v>25</v>
+      </c>
+      <c r="C252">
+        <v>68</v>
+      </c>
+      <c r="D252">
+        <v>81</v>
+      </c>
+      <c r="E252" t="s">
+        <v>149</v>
+      </c>
+      <c r="F252" t="s">
+        <v>150</v>
+      </c>
+      <c r="G252">
+        <v>68</v>
+      </c>
+      <c r="H252" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>449</v>
+      </c>
+      <c r="B253" t="s">
+        <v>64</v>
+      </c>
+      <c r="C253">
+        <v>18</v>
+      </c>
+      <c r="D253">
+        <v>18</v>
+      </c>
+      <c r="E253" t="s">
+        <v>332</v>
+      </c>
+      <c r="F253" t="s">
+        <v>333</v>
+      </c>
+      <c r="G253">
+        <v>18</v>
+      </c>
+      <c r="H253" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>450</v>
+      </c>
+      <c r="B254" t="s">
+        <v>109</v>
+      </c>
+      <c r="C254">
+        <v>66</v>
+      </c>
+      <c r="D254">
+        <v>34</v>
+      </c>
+      <c r="E254" t="s">
+        <v>345</v>
+      </c>
+      <c r="F254" t="s">
+        <v>346</v>
+      </c>
+      <c r="G254">
+        <v>66</v>
+      </c>
+      <c r="H254" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>451</v>
+      </c>
+      <c r="B255" t="s">
+        <v>25</v>
+      </c>
+      <c r="C255">
+        <v>68</v>
+      </c>
+      <c r="D255">
+        <v>16</v>
+      </c>
+      <c r="E255" t="s">
+        <v>149</v>
+      </c>
+      <c r="F255" t="s">
+        <v>150</v>
+      </c>
+      <c r="G255">
+        <v>68</v>
+      </c>
+      <c r="H255" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>452</v>
+      </c>
+      <c r="B256" t="s">
+        <v>89</v>
+      </c>
+      <c r="C256">
+        <v>64</v>
+      </c>
+      <c r="D256">
+        <v>14</v>
+      </c>
+      <c r="E256" t="s">
+        <v>106</v>
+      </c>
+      <c r="F256" t="s">
+        <v>107</v>
+      </c>
+      <c r="G256">
+        <v>64</v>
+      </c>
+      <c r="H256" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>453</v>
+      </c>
+      <c r="B257" t="s">
+        <v>16</v>
+      </c>
+      <c r="C257">
+        <v>25</v>
+      </c>
+      <c r="D257">
+        <v>5</v>
+      </c>
+      <c r="E257" t="s">
+        <v>17</v>
+      </c>
+      <c r="F257" t="s">
+        <v>18</v>
+      </c>
+      <c r="G257">
+        <v>25</v>
+      </c>
+      <c r="H257" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>454</v>
+      </c>
+      <c r="B258" t="s">
+        <v>11</v>
+      </c>
+      <c r="C258">
+        <v>74</v>
+      </c>
+      <c r="D258">
+        <v>5</v>
+      </c>
+      <c r="E258"/>
+      <c r="F258"/>
+      <c r="G258"/>
+      <c r="H258"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>455</v>
+      </c>
+      <c r="B259" t="s">
+        <v>25</v>
+      </c>
+      <c r="C259">
+        <v>67</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259" t="s">
+        <v>227</v>
+      </c>
+      <c r="F259" t="s">
+        <v>228</v>
+      </c>
+      <c r="G259">
+        <v>67</v>
+      </c>
+      <c r="H259" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>456</v>
+      </c>
+      <c r="B260" t="s">
+        <v>35</v>
+      </c>
+      <c r="C260">
+        <v>92</v>
+      </c>
+      <c r="D260">
+        <v>15</v>
+      </c>
+      <c r="E260" t="s">
+        <v>122</v>
+      </c>
+      <c r="F260" t="s">
+        <v>123</v>
+      </c>
+      <c r="G260">
+        <v>92</v>
+      </c>
+      <c r="H260" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>457</v>
+      </c>
+      <c r="B261" t="s">
+        <v>31</v>
+      </c>
+      <c r="C261">
+        <v>83</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+      <c r="E261" t="s">
+        <v>32</v>
+      </c>
+      <c r="F261" t="s">
+        <v>33</v>
+      </c>
+      <c r="G261">
+        <v>83</v>
+      </c>
+      <c r="H261" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>458</v>
+      </c>
+      <c r="B262" t="s">
+        <v>93</v>
+      </c>
+      <c r="C262">
+        <v>22</v>
+      </c>
+      <c r="D262">
+        <v>6</v>
+      </c>
+      <c r="E262" t="s">
+        <v>230</v>
+      </c>
+      <c r="F262" t="s">
+        <v>231</v>
+      </c>
+      <c r="G262">
+        <v>22</v>
+      </c>
+      <c r="H262" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>459</v>
+      </c>
+      <c r="B263" t="s">
+        <v>20</v>
+      </c>
+      <c r="C263">
+        <v>87</v>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+      <c r="E263" t="s">
+        <v>21</v>
+      </c>
+      <c r="F263" t="s">
+        <v>22</v>
+      </c>
+      <c r="G263">
+        <v>87</v>
+      </c>
+      <c r="H263" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>460</v>
+      </c>
+      <c r="B264" t="s">
+        <v>9</v>
+      </c>
+      <c r="C264">
+        <v>59</v>
+      </c>
+      <c r="D264">
+        <v>26</v>
+      </c>
+      <c r="E264" t="s">
+        <v>152</v>
+      </c>
+      <c r="F264" t="s">
+        <v>153</v>
+      </c>
+      <c r="G264">
+        <v>59</v>
+      </c>
+      <c r="H264" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>461</v>
+      </c>
+      <c r="B265" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265">
+        <v>69</v>
+      </c>
+      <c r="D265">
+        <v>34</v>
+      </c>
+      <c r="E265" t="s">
+        <v>12</v>
+      </c>
+      <c r="F265" t="s">
+        <v>13</v>
+      </c>
+      <c r="G265">
+        <v>69</v>
+      </c>
+      <c r="H265" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>462</v>
+      </c>
+      <c r="B266" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266">
+        <v>42</v>
+      </c>
+      <c r="D266">
+        <v>5</v>
+      </c>
+      <c r="E266" t="s">
+        <v>234</v>
+      </c>
+      <c r="F266" t="s">
+        <v>235</v>
+      </c>
+      <c r="G266">
+        <v>42</v>
+      </c>
+      <c r="H266" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>463</v>
+      </c>
+      <c r="B267" t="s">
+        <v>46</v>
+      </c>
+      <c r="C267">
+        <v>85</v>
+      </c>
+      <c r="D267">
+        <v>17</v>
+      </c>
+      <c r="E267" t="s">
+        <v>47</v>
+      </c>
+      <c r="F267" t="s">
+        <v>48</v>
+      </c>
+      <c r="G267">
+        <v>85</v>
+      </c>
+      <c r="H267" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>464</v>
+      </c>
+      <c r="B268" t="s">
+        <v>16</v>
+      </c>
+      <c r="C268">
+        <v>71</v>
+      </c>
+      <c r="D268">
+        <v>37</v>
+      </c>
+      <c r="E268" t="s">
+        <v>352</v>
+      </c>
+      <c r="F268" t="s">
+        <v>353</v>
+      </c>
+      <c r="G268">
+        <v>71</v>
+      </c>
+      <c r="H268" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>465</v>
+      </c>
+      <c r="B269" t="s">
+        <v>145</v>
+      </c>
+      <c r="C269">
+        <v>50</v>
+      </c>
+      <c r="D269">
+        <v>24</v>
+      </c>
+      <c r="E269" t="s">
+        <v>146</v>
+      </c>
+      <c r="F269" t="s">
+        <v>147</v>
+      </c>
+      <c r="G269">
+        <v>50</v>
+      </c>
+      <c r="H269" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>466</v>
+      </c>
+      <c r="B270" t="s">
+        <v>20</v>
+      </c>
+      <c r="C270">
+        <v>17</v>
+      </c>
+      <c r="D270">
+        <v>49</v>
+      </c>
+      <c r="E270" t="s">
+        <v>467</v>
+      </c>
+      <c r="F270" t="s">
+        <v>468</v>
+      </c>
+      <c r="G270">
+        <v>17</v>
+      </c>
+      <c r="H270" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>469</v>
+      </c>
+      <c r="B271" t="s">
+        <v>31</v>
+      </c>
+      <c r="C271">
+        <v>98</v>
+      </c>
+      <c r="D271">
+        <v>5</v>
+      </c>
+      <c r="E271"/>
+      <c r="F271"/>
+      <c r="G271"/>
+      <c r="H271"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>470</v>
+      </c>
+      <c r="B272" t="s">
+        <v>31</v>
+      </c>
+      <c r="C272">
+        <v>13</v>
+      </c>
+      <c r="D272">
+        <v>30</v>
+      </c>
+      <c r="E272" t="s">
+        <v>285</v>
+      </c>
+      <c r="F272" t="s">
+        <v>286</v>
+      </c>
+      <c r="G272">
+        <v>13</v>
+      </c>
+      <c r="H272" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>471</v>
+      </c>
+      <c r="B273" t="s">
+        <v>20</v>
+      </c>
+      <c r="C273">
+        <v>17</v>
+      </c>
+      <c r="D273">
+        <v>106</v>
+      </c>
+      <c r="E273" t="s">
+        <v>78</v>
+      </c>
+      <c r="F273" t="s">
+        <v>79</v>
+      </c>
+      <c r="G273">
+        <v>17</v>
+      </c>
+      <c r="H273" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>472</v>
+      </c>
+      <c r="B274" t="s">
+        <v>31</v>
+      </c>
+      <c r="C274">
+        <v>6</v>
+      </c>
+      <c r="D274">
+        <v>8</v>
+      </c>
+      <c r="E274" t="s">
+        <v>187</v>
+      </c>
+      <c r="F274" t="s">
+        <v>188</v>
+      </c>
+      <c r="G274">
+        <v>6</v>
+      </c>
+      <c r="H274" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>473</v>
+      </c>
+      <c r="B275" t="s">
+        <v>31</v>
+      </c>
+      <c r="C275">
+        <v>6</v>
+      </c>
+      <c r="D275">
+        <v>41</v>
+      </c>
+      <c r="E275" t="s">
+        <v>187</v>
+      </c>
+      <c r="F275" t="s">
+        <v>188</v>
+      </c>
+      <c r="G275">
+        <v>6</v>
+      </c>
+      <c r="H275" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>474</v>
+      </c>
+      <c r="B276" t="s">
+        <v>93</v>
+      </c>
+      <c r="C276">
+        <v>29</v>
+      </c>
+      <c r="D276">
+        <v>27</v>
+      </c>
+      <c r="E276" t="s">
+        <v>252</v>
+      </c>
+      <c r="F276" t="s">
+        <v>253</v>
+      </c>
+      <c r="G276">
+        <v>29</v>
+      </c>
+      <c r="H276" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>475</v>
+      </c>
+      <c r="B277" t="s">
+        <v>109</v>
+      </c>
+      <c r="C277">
+        <v>12</v>
+      </c>
+      <c r="D277">
+        <v>11</v>
+      </c>
+      <c r="E277" t="s">
+        <v>132</v>
+      </c>
+      <c r="F277" t="s">
+        <v>133</v>
+      </c>
+      <c r="G277">
+        <v>12</v>
+      </c>
+      <c r="H277" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>476</v>
+      </c>
+      <c r="B278" t="s">
+        <v>145</v>
+      </c>
+      <c r="C278">
+        <v>27</v>
+      </c>
+      <c r="D278">
+        <v>39</v>
+      </c>
+      <c r="E278" t="s">
+        <v>184</v>
+      </c>
+      <c r="F278" t="s">
+        <v>185</v>
+      </c>
+      <c r="G278">
+        <v>27</v>
+      </c>
+      <c r="H278" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>477</v>
+      </c>
+      <c r="B279" t="s">
+        <v>46</v>
+      </c>
+      <c r="C279">
+        <v>44</v>
+      </c>
+      <c r="D279">
+        <v>16</v>
+      </c>
+      <c r="E279" t="s">
+        <v>103</v>
+      </c>
+      <c r="F279" t="s">
+        <v>104</v>
+      </c>
+      <c r="G279">
+        <v>44</v>
+      </c>
+      <c r="H279" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>478</v>
+      </c>
+      <c r="B280" t="s">
+        <v>93</v>
+      </c>
+      <c r="C280">
+        <v>56</v>
+      </c>
+      <c r="D280">
+        <v>24</v>
+      </c>
+      <c r="E280" t="s">
+        <v>242</v>
+      </c>
+      <c r="F280" t="s">
+        <v>243</v>
+      </c>
+      <c r="G280">
+        <v>56</v>
+      </c>
+      <c r="H280" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>479</v>
+      </c>
+      <c r="B281" t="s">
+        <v>145</v>
+      </c>
+      <c r="C281">
+        <v>61</v>
+      </c>
+      <c r="D281">
+        <v>35</v>
+      </c>
+      <c r="E281" t="s">
+        <v>223</v>
+      </c>
+      <c r="F281" t="s">
+        <v>224</v>
+      </c>
+      <c r="G281">
+        <v>61</v>
+      </c>
+      <c r="H281" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>480</v>
+      </c>
+      <c r="B282" t="s">
+        <v>89</v>
+      </c>
+      <c r="C282">
+        <v>64</v>
+      </c>
+      <c r="D282">
+        <v>14</v>
+      </c>
+      <c r="E282" t="s">
+        <v>106</v>
+      </c>
+      <c r="F282" t="s">
+        <v>107</v>
+      </c>
+      <c r="G282">
+        <v>64</v>
+      </c>
+      <c r="H282" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>481</v>
+      </c>
+      <c r="B283" t="s">
+        <v>31</v>
+      </c>
+      <c r="C283">
+        <v>84</v>
+      </c>
+      <c r="D283">
+        <v>24</v>
+      </c>
+      <c r="E283" t="s">
+        <v>436</v>
+      </c>
+      <c r="F283" t="s">
+        <v>437</v>
+      </c>
+      <c r="G283">
+        <v>84</v>
+      </c>
+      <c r="H283" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>482</v>
+      </c>
+      <c r="B284" t="s">
+        <v>64</v>
+      </c>
+      <c r="C284">
+        <v>41</v>
+      </c>
+      <c r="D284">
+        <v>22</v>
+      </c>
+      <c r="E284" t="s">
+        <v>100</v>
+      </c>
+      <c r="F284" t="s">
+        <v>101</v>
+      </c>
+      <c r="G284">
+        <v>41</v>
+      </c>
+      <c r="H284" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>483</v>
+      </c>
+      <c r="B285" t="s">
+        <v>46</v>
+      </c>
+      <c r="C285">
+        <v>49</v>
+      </c>
+      <c r="D285">
+        <v>12</v>
+      </c>
+      <c r="E285" t="s">
+        <v>56</v>
+      </c>
+      <c r="F285" t="s">
+        <v>57</v>
+      </c>
+      <c r="G285">
+        <v>49</v>
+      </c>
+      <c r="H285" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>484</v>
+      </c>
+      <c r="B286" t="s">
+        <v>11</v>
+      </c>
+      <c r="C286">
+        <v>42</v>
+      </c>
+      <c r="D286">
+        <v>17</v>
+      </c>
+      <c r="E286" t="s">
+        <v>234</v>
+      </c>
+      <c r="F286" t="s">
+        <v>235</v>
+      </c>
+      <c r="G286">
+        <v>42</v>
+      </c>
+      <c r="H286" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>485</v>
+      </c>
+      <c r="B287" t="s">
+        <v>25</v>
+      </c>
+      <c r="C287">
+        <v>51</v>
+      </c>
+      <c r="D287">
+        <v>27</v>
+      </c>
+      <c r="E287" t="s">
+        <v>486</v>
+      </c>
+      <c r="F287" t="s">
+        <v>487</v>
+      </c>
+      <c r="G287">
+        <v>51</v>
+      </c>
+      <c r="H287" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>488</v>
+      </c>
+      <c r="B288" t="s">
+        <v>109</v>
+      </c>
+      <c r="C288">
+        <v>34</v>
+      </c>
+      <c r="D288">
+        <v>11</v>
+      </c>
+      <c r="E288" t="s">
+        <v>159</v>
+      </c>
+      <c r="F288" t="s">
+        <v>160</v>
+      </c>
+      <c r="G288">
+        <v>34</v>
+      </c>
+      <c r="H288" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>489</v>
+      </c>
+      <c r="B289" t="s">
+        <v>46</v>
+      </c>
+      <c r="C289">
+        <v>44</v>
+      </c>
+      <c r="D289">
+        <v>28</v>
+      </c>
+      <c r="E289" t="s">
+        <v>73</v>
+      </c>
+      <c r="F289" t="s">
+        <v>74</v>
+      </c>
+      <c r="G289">
+        <v>44</v>
+      </c>
+      <c r="H289" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>490</v>
+      </c>
+      <c r="B290" t="s">
+        <v>64</v>
+      </c>
+      <c r="C290">
+        <v>45</v>
+      </c>
+      <c r="D290">
+        <v>20</v>
+      </c>
+      <c r="E290" t="s">
+        <v>68</v>
+      </c>
+      <c r="F290" t="s">
+        <v>69</v>
+      </c>
+      <c r="G290">
+        <v>45</v>
+      </c>
+      <c r="H290" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>491</v>
+      </c>
+      <c r="B291" t="s">
+        <v>31</v>
+      </c>
+      <c r="C291">
+        <v>83</v>
+      </c>
+      <c r="D291">
+        <v>41</v>
+      </c>
+      <c r="E291" t="s">
+        <v>32</v>
+      </c>
+      <c r="F291" t="s">
+        <v>33</v>
+      </c>
+      <c r="G291">
+        <v>83</v>
+      </c>
+      <c r="H291" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>492</v>
+      </c>
+      <c r="B292" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292">
+        <v>86</v>
+      </c>
+      <c r="D292">
+        <v>18</v>
+      </c>
+      <c r="E292" t="s">
+        <v>39</v>
+      </c>
+      <c r="F292" t="s">
+        <v>40</v>
+      </c>
+      <c r="G292">
+        <v>86</v>
+      </c>
+      <c r="H292" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>493</v>
+      </c>
+      <c r="B293" t="s">
+        <v>11</v>
+      </c>
+      <c r="C293">
+        <v>73</v>
+      </c>
+      <c r="D293">
+        <v>13</v>
+      </c>
+      <c r="E293" t="s">
+        <v>494</v>
+      </c>
+      <c r="F293" t="s">
+        <v>495</v>
+      </c>
+      <c r="G293">
+        <v>73</v>
+      </c>
+      <c r="H293" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>496</v>
+      </c>
+      <c r="B294" t="s">
+        <v>93</v>
+      </c>
+      <c r="C294">
+        <v>35</v>
+      </c>
+      <c r="D294">
+        <v>102</v>
+      </c>
+      <c r="E294" t="s">
+        <v>94</v>
+      </c>
+      <c r="F294" t="s">
+        <v>95</v>
+      </c>
+      <c r="G294">
+        <v>35</v>
+      </c>
+      <c r="H294" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>497</v>
+      </c>
+      <c r="B295" t="s">
+        <v>46</v>
+      </c>
+      <c r="C295">
+        <v>44</v>
+      </c>
+      <c r="D295">
+        <v>85</v>
+      </c>
+      <c r="E295" t="s">
+        <v>103</v>
+      </c>
+      <c r="F295" t="s">
+        <v>104</v>
+      </c>
+      <c r="G295">
+        <v>44</v>
+      </c>
+      <c r="H295" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>498</v>
+      </c>
+      <c r="B296" t="s">
+        <v>46</v>
+      </c>
+      <c r="C296">
+        <v>49</v>
+      </c>
+      <c r="D296">
+        <v>5</v>
+      </c>
+      <c r="E296" t="s">
+        <v>56</v>
+      </c>
+      <c r="F296" t="s">
+        <v>57</v>
+      </c>
+      <c r="G296">
+        <v>49</v>
+      </c>
+      <c r="H296" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>499</v>
+      </c>
+      <c r="B297" t="s">
+        <v>89</v>
+      </c>
+      <c r="C297">
+        <v>47</v>
+      </c>
+      <c r="D297">
+        <v>17</v>
+      </c>
+      <c r="E297" t="s">
+        <v>500</v>
+      </c>
+      <c r="F297" t="s">
+        <v>501</v>
+      </c>
+      <c r="G297">
+        <v>47</v>
+      </c>
+      <c r="H297" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>502</v>
+      </c>
+      <c r="B298" t="s">
+        <v>89</v>
+      </c>
+      <c r="C298">
+        <v>33</v>
+      </c>
+      <c r="D298">
+        <v>19</v>
+      </c>
+      <c r="E298" t="s">
+        <v>90</v>
+      </c>
+      <c r="F298" t="s">
+        <v>91</v>
+      </c>
+      <c r="G298">
+        <v>33</v>
+      </c>
+      <c r="H298" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>503</v>
+      </c>
+      <c r="B299" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299">
+        <v>63</v>
+      </c>
+      <c r="D299">
+        <v>28</v>
+      </c>
+      <c r="E299" t="s">
+        <v>129</v>
+      </c>
+      <c r="F299" t="s">
+        <v>130</v>
+      </c>
+      <c r="G299">
+        <v>63</v>
+      </c>
+      <c r="H299" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>504</v>
+      </c>
+      <c r="B300" t="s">
+        <v>109</v>
+      </c>
+      <c r="C300">
+        <v>31</v>
+      </c>
+      <c r="D300">
+        <v>14</v>
+      </c>
+      <c r="E300" t="s">
+        <v>110</v>
+      </c>
+      <c r="F300" t="s">
+        <v>111</v>
+      </c>
+      <c r="G300">
+        <v>31</v>
+      </c>
+      <c r="H300" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>505</v>
+      </c>
+      <c r="B301" t="s">
+        <v>93</v>
+      </c>
+      <c r="C301">
+        <v>22</v>
+      </c>
+      <c r="D301">
+        <v>16</v>
+      </c>
+      <c r="E301" t="s">
+        <v>230</v>
+      </c>
+      <c r="F301" t="s">
+        <v>231</v>
+      </c>
+      <c r="G301">
+        <v>22</v>
+      </c>
+      <c r="H301" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>506</v>
+      </c>
+      <c r="B302" t="s">
+        <v>89</v>
+      </c>
+      <c r="C302">
+        <v>40</v>
+      </c>
+      <c r="D302">
+        <v>21</v>
+      </c>
+      <c r="E302" t="s">
+        <v>328</v>
+      </c>
+      <c r="F302" t="s">
+        <v>329</v>
+      </c>
+      <c r="G302">
+        <v>40</v>
+      </c>
+      <c r="H302" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>507</v>
+      </c>
+      <c r="B303" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303">
+        <v>2</v>
+      </c>
+      <c r="D303">
+        <v>36</v>
+      </c>
+      <c r="E303"/>
+      <c r="F303"/>
+      <c r="G303"/>
+      <c r="H303"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>508</v>
+      </c>
+      <c r="B304" t="s">
+        <v>35</v>
+      </c>
+      <c r="C304">
+        <v>91</v>
+      </c>
+      <c r="D304">
+        <v>106</v>
+      </c>
+      <c r="E304" t="s">
+        <v>142</v>
+      </c>
+      <c r="F304" t="s">
+        <v>143</v>
+      </c>
+      <c r="G304">
+        <v>91</v>
+      </c>
+      <c r="H304" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>509</v>
+      </c>
+      <c r="B305" t="s">
+        <v>35</v>
+      </c>
+      <c r="C305">
+        <v>75</v>
+      </c>
+      <c r="D305">
+        <v>2</v>
+      </c>
+      <c r="E305" t="s">
+        <v>84</v>
+      </c>
+      <c r="F305" t="s">
+        <v>85</v>
+      </c>
+      <c r="G305">
+        <v>75</v>
+      </c>
+      <c r="H305" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>510</v>
+      </c>
+      <c r="B306" t="s">
+        <v>16</v>
+      </c>
+      <c r="C306">
+        <v>90</v>
+      </c>
+      <c r="D306">
+        <v>113</v>
+      </c>
+      <c r="E306" t="s">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>18</v>
+      </c>
+      <c r="G306">
+        <v>25</v>
+      </c>
+      <c r="H306" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>511</v>
+      </c>
+      <c r="B307" t="s">
+        <v>25</v>
+      </c>
+      <c r="C307">
+        <v>54</v>
+      </c>
+      <c r="D307">
+        <v>40</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+      <c r="G307">
+        <v>57</v>
+      </c>
+      <c r="H307" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>512</v>
+      </c>
+      <c r="B308" t="s">
+        <v>64</v>
+      </c>
+      <c r="C308">
+        <v>45</v>
+      </c>
+      <c r="D308">
+        <v>17</v>
+      </c>
+      <c r="E308" t="s">
+        <v>68</v>
+      </c>
+      <c r="F308" t="s">
+        <v>69</v>
+      </c>
+      <c r="G308">
+        <v>45</v>
+      </c>
+      <c r="H308" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>513</v>
+      </c>
+      <c r="B309" t="s">
+        <v>46</v>
+      </c>
+      <c r="C309">
+        <v>44</v>
+      </c>
+      <c r="D309">
+        <v>9</v>
+      </c>
+      <c r="E309" t="s">
+        <v>103</v>
+      </c>
+      <c r="F309" t="s">
+        <v>104</v>
+      </c>
+      <c r="G309">
+        <v>44</v>
+      </c>
+      <c r="H309" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>514</v>
+      </c>
+      <c r="B310" t="s">
+        <v>11</v>
+      </c>
+      <c r="C310">
+        <v>3</v>
+      </c>
+      <c r="D310">
+        <v>19</v>
+      </c>
+      <c r="E310" t="s">
+        <v>515</v>
+      </c>
+      <c r="F310" t="s">
+        <v>516</v>
+      </c>
+      <c r="G310">
+        <v>3</v>
+      </c>
+      <c r="H310" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>517</v>
+      </c>
+      <c r="B311" t="s">
+        <v>11</v>
+      </c>
+      <c r="C311">
+        <v>73</v>
+      </c>
+      <c r="D311">
+        <v>50</v>
+      </c>
+      <c r="E311" t="s">
+        <v>494</v>
+      </c>
+      <c r="F311" t="s">
+        <v>495</v>
+      </c>
+      <c r="G311">
+        <v>73</v>
+      </c>
+      <c r="H311" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>518</v>
+      </c>
+      <c r="B312" t="s">
+        <v>64</v>
+      </c>
+      <c r="C312">
+        <v>41</v>
+      </c>
+      <c r="D312">
+        <v>10</v>
+      </c>
+      <c r="E312" t="s">
+        <v>100</v>
+      </c>
+      <c r="F312" t="s">
+        <v>101</v>
+      </c>
+      <c r="G312">
+        <v>41</v>
+      </c>
+      <c r="H312" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>519</v>
+      </c>
+      <c r="B313" t="s">
+        <v>9</v>
+      </c>
+      <c r="C313">
+        <v>60</v>
+      </c>
+      <c r="D313">
+        <v>14</v>
+      </c>
+      <c r="E313" t="s">
+        <v>303</v>
+      </c>
+      <c r="F313" t="s">
+        <v>304</v>
+      </c>
+      <c r="G313">
+        <v>60</v>
+      </c>
+      <c r="H313" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>520</v>
+      </c>
+      <c r="B314" t="s">
+        <v>31</v>
+      </c>
+      <c r="C314">
+        <v>83</v>
+      </c>
+      <c r="D314">
+        <v>2</v>
+      </c>
+      <c r="E314" t="s">
+        <v>32</v>
+      </c>
+      <c r="F314" t="s">
+        <v>33</v>
+      </c>
+      <c r="G314">
+        <v>83</v>
+      </c>
+      <c r="H314" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>521</v>
+      </c>
+      <c r="B315" t="s">
+        <v>11</v>
+      </c>
+      <c r="C315">
+        <v>3</v>
+      </c>
+      <c r="D315">
+        <v>24</v>
+      </c>
+      <c r="E315" t="s">
+        <v>387</v>
+      </c>
+      <c r="F315" t="s">
+        <v>388</v>
+      </c>
+      <c r="G315">
+        <v>3</v>
+      </c>
+      <c r="H315" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>522</v>
+      </c>
+      <c r="B316" t="s">
+        <v>25</v>
+      </c>
+      <c r="C316">
+        <v>8</v>
+      </c>
+      <c r="D316">
+        <v>11</v>
+      </c>
+      <c r="E316" t="s">
+        <v>114</v>
+      </c>
+      <c r="F316" t="s">
+        <v>115</v>
+      </c>
+      <c r="G316">
+        <v>8</v>
+      </c>
+      <c r="H316" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>523</v>
+      </c>
+      <c r="B317" t="s">
+        <v>89</v>
+      </c>
+      <c r="C317">
+        <v>40</v>
+      </c>
+      <c r="D317">
+        <v>29</v>
+      </c>
+      <c r="E317" t="s">
+        <v>328</v>
+      </c>
+      <c r="F317" t="s">
+        <v>329</v>
+      </c>
+      <c r="G317">
+        <v>40</v>
+      </c>
+      <c r="H317" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>524</v>
+      </c>
+      <c r="B318" t="s">
+        <v>9</v>
+      </c>
+      <c r="C318">
+        <v>59</v>
+      </c>
+      <c r="D318">
+        <v>43</v>
+      </c>
+      <c r="E318" t="s">
+        <v>525</v>
+      </c>
+      <c r="F318" t="s">
+        <v>526</v>
+      </c>
+      <c r="G318">
+        <v>59</v>
+      </c>
+      <c r="H318" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>527</v>
+      </c>
+      <c r="B319" t="s">
+        <v>25</v>
+      </c>
+      <c r="C319">
+        <v>51</v>
+      </c>
+      <c r="D319">
+        <v>13</v>
+      </c>
+      <c r="E319" t="s">
+        <v>206</v>
+      </c>
+      <c r="F319" t="s">
+        <v>207</v>
+      </c>
+      <c r="G319">
+        <v>51</v>
+      </c>
+      <c r="H319" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>528</v>
+      </c>
+      <c r="B320" t="s">
+        <v>423</v>
+      </c>
+      <c r="C320">
+        <v>971</v>
+      </c>
+      <c r="D320">
+        <v>14</v>
+      </c>
+      <c r="E320"/>
+      <c r="F320"/>
+      <c r="G320"/>
+      <c r="H320"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>529</v>
+      </c>
+      <c r="B321" t="s">
+        <v>11</v>
+      </c>
+      <c r="C321">
+        <v>3</v>
+      </c>
+      <c r="D321">
+        <v>13</v>
+      </c>
+      <c r="E321" t="s">
+        <v>387</v>
+      </c>
+      <c r="F321" t="s">
+        <v>388</v>
+      </c>
+      <c r="G321">
+        <v>3</v>
+      </c>
+      <c r="H321" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>530</v>
+      </c>
+      <c r="B322" t="s">
+        <v>89</v>
+      </c>
+      <c r="C322">
+        <v>24</v>
+      </c>
+      <c r="D322">
+        <v>31</v>
+      </c>
+      <c r="E322" t="s">
+        <v>321</v>
+      </c>
+      <c r="F322" t="s">
+        <v>322</v>
+      </c>
+      <c r="G322">
+        <v>24</v>
+      </c>
+      <c r="H322" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>531</v>
+      </c>
+      <c r="B323" t="s">
+        <v>31</v>
+      </c>
+      <c r="C323">
+        <v>84</v>
+      </c>
+      <c r="D323">
+        <v>26</v>
+      </c>
+      <c r="E323" t="s">
+        <v>193</v>
+      </c>
+      <c r="F323" t="s">
+        <v>194</v>
+      </c>
+      <c r="G323">
+        <v>84</v>
+      </c>
+      <c r="H323" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>532</v>
+      </c>
+      <c r="B324" t="s">
+        <v>89</v>
+      </c>
+      <c r="C324">
+        <v>47</v>
+      </c>
+      <c r="D324">
+        <v>7</v>
+      </c>
+      <c r="E324" t="s">
+        <v>500</v>
+      </c>
+      <c r="F324" t="s">
+        <v>501</v>
+      </c>
+      <c r="G324">
+        <v>47</v>
+      </c>
+      <c r="H324" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>533</v>
+      </c>
+      <c r="B325" t="s">
+        <v>35</v>
+      </c>
+      <c r="C325">
+        <v>92</v>
+      </c>
+      <c r="D325">
+        <v>5</v>
+      </c>
+      <c r="E325" t="s">
+        <v>122</v>
+      </c>
+      <c r="F325" t="s">
+        <v>123</v>
+      </c>
+      <c r="G325">
+        <v>92</v>
+      </c>
+      <c r="H325" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>534</v>
+      </c>
+      <c r="B326" t="s">
+        <v>109</v>
+      </c>
+      <c r="C326">
+        <v>31</v>
+      </c>
+      <c r="D326">
+        <v>44</v>
+      </c>
+      <c r="E326" t="s">
+        <v>110</v>
+      </c>
+      <c r="F326" t="s">
+        <v>111</v>
+      </c>
+      <c r="G326">
+        <v>31</v>
+      </c>
+      <c r="H326" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>535</v>
+      </c>
+      <c r="B327" t="s">
+        <v>89</v>
+      </c>
+      <c r="C327">
+        <v>24</v>
+      </c>
+      <c r="D327">
+        <v>20</v>
+      </c>
+      <c r="E327" t="s">
+        <v>321</v>
+      </c>
+      <c r="F327" t="s">
+        <v>322</v>
+      </c>
+      <c r="G327">
+        <v>24</v>
+      </c>
+      <c r="H327" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>536</v>
+      </c>
+      <c r="B328" t="s">
+        <v>64</v>
+      </c>
+      <c r="C328">
+        <v>18</v>
+      </c>
+      <c r="D328">
+        <v>35</v>
+      </c>
+      <c r="E328" t="s">
+        <v>332</v>
+      </c>
+      <c r="F328" t="s">
+        <v>333</v>
+      </c>
+      <c r="G328">
+        <v>18</v>
+      </c>
+      <c r="H328" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>537</v>
+      </c>
+      <c r="B329" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329">
+        <v>69</v>
+      </c>
+      <c r="D329">
+        <v>70</v>
+      </c>
+      <c r="E329" t="s">
+        <v>12</v>
+      </c>
+      <c r="F329" t="s">
+        <v>13</v>
+      </c>
+      <c r="G329">
+        <v>69</v>
+      </c>
+      <c r="H329" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>538</v>
+      </c>
+      <c r="B330" t="s">
+        <v>109</v>
+      </c>
+      <c r="C330">
+        <v>31</v>
+      </c>
+      <c r="D330">
+        <v>26</v>
+      </c>
+      <c r="E330" t="s">
+        <v>110</v>
+      </c>
+      <c r="F330" t="s">
+        <v>111</v>
+      </c>
+      <c r="G330">
+        <v>31</v>
+      </c>
+      <c r="H330" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>539</v>
+      </c>
+      <c r="B331" t="s">
+        <v>20</v>
+      </c>
+      <c r="C331">
+        <v>17</v>
+      </c>
+      <c r="D331">
+        <v>36</v>
+      </c>
+      <c r="E331" t="s">
+        <v>78</v>
+      </c>
+      <c r="F331" t="s">
+        <v>79</v>
+      </c>
+      <c r="G331">
+        <v>17</v>
+      </c>
+      <c r="H331" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>540</v>
+      </c>
+      <c r="B332" t="s">
+        <v>25</v>
+      </c>
+      <c r="C332">
+        <v>10</v>
+      </c>
+      <c r="D332">
+        <v>24</v>
+      </c>
+      <c r="E332" t="s">
+        <v>541</v>
+      </c>
+      <c r="F332" t="s">
+        <v>542</v>
+      </c>
+      <c r="G332">
+        <v>10</v>
+      </c>
+      <c r="H332" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>543</v>
+      </c>
+      <c r="B333" t="s">
+        <v>16</v>
+      </c>
+      <c r="C333">
+        <v>58</v>
+      </c>
+      <c r="D333">
+        <v>12</v>
+      </c>
+      <c r="E333"/>
+      <c r="F333"/>
+      <c r="G333"/>
+      <c r="H333"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>544</v>
+      </c>
+      <c r="B334" t="s">
+        <v>64</v>
+      </c>
+      <c r="C334">
+        <v>45</v>
+      </c>
+      <c r="D334">
+        <v>21</v>
+      </c>
+      <c r="E334" t="s">
+        <v>68</v>
+      </c>
+      <c r="F334" t="s">
+        <v>69</v>
+      </c>
+      <c r="G334">
+        <v>45</v>
+      </c>
+      <c r="H334" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>545</v>
+      </c>
+      <c r="B335" t="s">
+        <v>35</v>
+      </c>
+      <c r="C335">
+        <v>77</v>
+      </c>
+      <c r="D335">
+        <v>37</v>
+      </c>
+      <c r="E335" t="s">
+        <v>50</v>
+      </c>
+      <c r="F335" t="s">
+        <v>51</v>
+      </c>
+      <c r="G335">
+        <v>77</v>
+      </c>
+      <c r="H335" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>546</v>
+      </c>
+      <c r="B336" t="s">
+        <v>31</v>
+      </c>
+      <c r="C336">
+        <v>83</v>
+      </c>
+      <c r="D336">
+        <v>32</v>
+      </c>
+      <c r="E336" t="s">
+        <v>32</v>
+      </c>
+      <c r="F336" t="s">
+        <v>33</v>
+      </c>
+      <c r="G336">
+        <v>83</v>
+      </c>
+      <c r="H336" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>547</v>
+      </c>
+      <c r="B337" t="s">
+        <v>109</v>
+      </c>
+      <c r="C337">
+        <v>30</v>
+      </c>
+      <c r="D337">
+        <v>39</v>
+      </c>
+      <c r="E337" t="s">
+        <v>201</v>
+      </c>
+      <c r="F337" t="s">
+        <v>202</v>
+      </c>
+      <c r="G337">
+        <v>30</v>
+      </c>
+      <c r="H337" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>548</v>
+      </c>
+      <c r="B338" t="s">
+        <v>9</v>
+      </c>
+      <c r="C338">
+        <v>59</v>
+      </c>
+      <c r="D338">
+        <v>20</v>
+      </c>
+      <c r="E338" t="s">
+        <v>152</v>
+      </c>
+      <c r="F338" t="s">
+        <v>153</v>
+      </c>
+      <c r="G338">
+        <v>59</v>
+      </c>
+      <c r="H338" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>549</v>
+      </c>
+      <c r="B339" t="s">
+        <v>145</v>
+      </c>
+      <c r="C339">
+        <v>14</v>
+      </c>
+      <c r="D339">
+        <v>12</v>
+      </c>
+      <c r="E339" t="s">
+        <v>377</v>
+      </c>
+      <c r="F339" t="s">
+        <v>378</v>
+      </c>
+      <c r="G339">
+        <v>14</v>
+      </c>
+      <c r="H339" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>550</v>
+      </c>
+      <c r="B340" t="s">
+        <v>64</v>
+      </c>
+      <c r="C340">
+        <v>45</v>
+      </c>
+      <c r="D340">
+        <v>31</v>
+      </c>
+      <c r="E340" t="s">
+        <v>68</v>
+      </c>
+      <c r="F340" t="s">
+        <v>69</v>
+      </c>
+      <c r="G340">
+        <v>45</v>
+      </c>
+      <c r="H340" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>551</v>
+      </c>
+      <c r="B341" t="s">
+        <v>64</v>
+      </c>
+      <c r="C341">
+        <v>41</v>
+      </c>
+      <c r="D341">
+        <v>109</v>
+      </c>
+      <c r="E341" t="s">
+        <v>100</v>
+      </c>
+      <c r="F341" t="s">
+        <v>101</v>
+      </c>
+      <c r="G341">
+        <v>41</v>
+      </c>
+      <c r="H341" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>552</v>
+      </c>
+      <c r="B342" t="s">
+        <v>64</v>
+      </c>
+      <c r="C342">
+        <v>28</v>
+      </c>
+      <c r="D342">
+        <v>18</v>
+      </c>
+      <c r="E342" t="s">
+        <v>65</v>
+      </c>
+      <c r="F342" t="s">
+        <v>66</v>
+      </c>
+      <c r="G342">
+        <v>28</v>
+      </c>
+      <c r="H342" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>553</v>
+      </c>
+      <c r="B343" t="s">
+        <v>25</v>
+      </c>
+      <c r="C343">
+        <v>67</v>
+      </c>
+      <c r="D343">
+        <v>16</v>
+      </c>
+      <c r="E343" t="s">
+        <v>227</v>
+      </c>
+      <c r="F343" t="s">
+        <v>228</v>
+      </c>
+      <c r="G343">
+        <v>67</v>
+      </c>
+      <c r="H343" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>554</v>
+      </c>
+      <c r="B344" t="s">
+        <v>35</v>
+      </c>
+      <c r="C344">
+        <v>75</v>
+      </c>
+      <c r="D344">
+        <v>14</v>
+      </c>
+      <c r="E344" t="s">
+        <v>84</v>
+      </c>
+      <c r="F344" t="s">
+        <v>85</v>
+      </c>
+      <c r="G344">
+        <v>75</v>
+      </c>
+      <c r="H344" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
